--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="246">
   <si>
     <t>Metric</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Last updated</t>
   </si>
   <si>
-    <t>2026-10-12</t>
+    <t>2026-10-13</t>
   </si>
   <si>
     <t>Area</t>
@@ -154,10 +154,22 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>No parent-teacher messaging surface</t>
-  </si>
-  <si>
-    <t>A general direct-message API exists platform-wide, but nothing on the parent dashboard exposes it for contacting a teacher. Feature gap, not a bug.</t>
+    <t>No parent-to-school-admin messaging surface</t>
+  </si>
+  <si>
+    <t>A general direct-message API exists platform-wide, but nothing on the parent dashboard exposes it for contacting the school admin. Client confirmed this should go to the school admin, not individual teachers. Feature gap, not a bug — not yet built.</t>
+  </si>
+  <si>
+    <t>classroomAnalyticsRoutes.js had its admin gate commented out</t>
+  </si>
+  <si>
+    <t>getClassroomDashboard and exportClassroomSummary had NO auth check at all — anyone could view or export any classroom's full analytics. Found during the CSRF audit below. Restored the gate, properly path-scoped this time (an earlier, unscoped version of the fix briefly broke every /labs/* route for non-admins — caught live in verification before it was ever committed).</t>
+  </si>
+  <si>
+    <t>adminTestimonyRoutes.js toggle/delete had zero auth check</t>
+  </si>
+  <si>
+    <t>Anyone (logged in or not) could publish/unpublish or permanently delete any testimony. Found during the CSRF audit below. Added a router-wide admin gate.</t>
   </si>
   <si>
     <t>Public</t>
@@ -178,16 +190,16 @@
     <t>Cross-cutting</t>
   </si>
   <si>
-    <t>CSRF coverage is partial</t>
-  </si>
-  <si>
-    <t>Being added router-by-router per the project's own established pattern; some older routes remain unprotected.</t>
-  </si>
-  <si>
-    <t>Session cookie 'secure' flag is false</t>
-  </si>
-  <si>
-    <t>Should be enabled once the production domain is confirmed fully HTTPS end-to-end.</t>
+    <t>CSRF coverage was partial</t>
+  </si>
+  <si>
+    <t>Added CSRF protection to every authenticated-area router that was missing it (about, arduino components, testimonies, company, lab assets, announcements, newsletters, gallery admin, notifications, messages, profile update, labs). Scoped carefully per-router to avoid forcing a session for anonymous visitors on routers mixing public and admin routes (gallery, about, user). Two genuinely public, anonymous-only routers (announcements view/dismiss tracking, FAQ/testimony submission) are deliberately left unprotected — spam risk only, no privileged session to protect. Verified live: 28 checks covering every router touched.</t>
+  </si>
+  <si>
+    <t>Session cookie 'secure' flag was always false</t>
+  </si>
+  <si>
+    <t>Changed to 'auto' (express-session's proxy-aware mode) plus 'trust proxy' so Express correctly reads the X-Forwarded-Proto header Railway's TLS-terminating proxy sets. Cookie is now Secure in production (confirmed HTTPS end-to-end) while staying non-Secure for local/test servers over plain HTTP. Verified live both ways.</t>
   </si>
   <si>
     <t>Arcade</t>
@@ -1194,7 +1206,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1202,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1218,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1269,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1490,16 +1502,16 @@
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1507,41 +1519,69 @@
         <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>57</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1592,58 +1632,58 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1665,13 +1705,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -1679,13 +1719,13 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1693,898 +1733,898 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2592,13 +2632,13 @@
         <v>45</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2606,13 +2646,13 @@
         <v>45</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2620,13 +2660,13 @@
         <v>45</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2634,13 +2674,13 @@
         <v>45</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2648,13 +2688,13 @@
         <v>45</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2662,13 +2702,13 @@
         <v>45</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2676,13 +2716,13 @@
         <v>45</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2690,97 +2730,97 @@
         <v>45</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="249">
   <si>
     <t>Metric</t>
   </si>
@@ -572,6 +572,15 @@
   </si>
   <si>
     <t>I can learn embedded electronics safely and for free</t>
+  </si>
+  <si>
+    <t>upload my sketch straight to a real Arduino Uno plugged into my computer, without installing the Arduino IDE or any other app</t>
+  </si>
+  <si>
+    <t>once I do own a board, I can take what I built in the simulator and actually run it for real</t>
+  </si>
+  <si>
+    <t>Implemented this session — protocol verified in software against a simulated STK500 device (sync, programming, and a deliberate-failure verify check all behave correctly); not yet confirmed against a real Arduino Uno, since no hardware is available in this environment to test with</t>
   </si>
   <si>
     <t>submit a lab task attached to a lesson and get AI feedback</t>
@@ -1254,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1262,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1695,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2456,7 +2465,7 @@
         <v>187</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2464,13 +2473,13 @@
         <v>177</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>190</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2484,7 +2493,7 @@
         <v>192</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2492,10 +2501,10 @@
         <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>79</v>
@@ -2506,10 +2515,10 @@
         <v>177</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>79</v>
@@ -2520,10 +2529,10 @@
         <v>177</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>79</v>
@@ -2531,7 +2540,7 @@
     </row>
     <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>200</v>
@@ -2545,21 +2554,21 @@
     </row>
     <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>205</v>
@@ -2573,7 +2582,7 @@
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>208</v>
@@ -2582,18 +2591,18 @@
         <v>209</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>79</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>79</v>
@@ -2601,13 +2610,13 @@
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>79</v>
@@ -2615,13 +2624,13 @@
     </row>
     <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>79</v>
@@ -2629,13 +2638,13 @@
     </row>
     <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>45</v>
+        <v>202</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>79</v>
@@ -2646,10 +2655,10 @@
         <v>45</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>79</v>
@@ -2660,10 +2669,10 @@
         <v>45</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>79</v>
@@ -2674,13 +2683,13 @@
         <v>45</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>224</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2694,7 +2703,7 @@
         <v>226</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2702,10 +2711,10 @@
         <v>45</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>79</v>
@@ -2716,10 +2725,10 @@
         <v>45</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>79</v>
@@ -2730,10 +2739,10 @@
         <v>45</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>79</v>
@@ -2741,7 +2750,7 @@
     </row>
     <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>234</v>
@@ -2755,13 +2764,13 @@
     </row>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>79</v>
@@ -2769,13 +2778,13 @@
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>79</v>
@@ -2783,13 +2792,13 @@
     </row>
     <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>79</v>
@@ -2797,13 +2806,13 @@
     </row>
     <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>79</v>
@@ -2811,15 +2820,29 @@
     </row>
     <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>79</v>
       </c>
     </row>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="251">
   <si>
     <t>Metric</t>
   </si>
@@ -67,10 +67,16 @@
     <t>Student</t>
   </si>
   <si>
+    <t>Arduino Lab: circuit pan/zoom and Blocks mode became unclickable</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Self-inflicted regression: adding the shared page header to this lab (for its CSRF token, same session) pulled in a global, unscoped `canvas { width:100% !important }` CSS rule meant only for admin analytics charts — it stretched Blockly's normally-invisible internal measuring canvas into a giant overlay covering most of the page, silently eating every click/drag/scroll meant for the circuit canvas and the Blocks workspace underneath it. Same bug, already fixed once before for the standalone Blockly Lab; this port of that fix closes the gap. Also added genuine two-finger touch pinch-to-zoom for the circuit canvas (previously mouse/trackpad only) and made Blockly's pinch-zoom config explicit rather than implicit. Verified live: 8 checks covering hit-testing, mouse drag, Ctrl+wheel zoom, and a real two-finger touch pinch gesture.</t>
+  </si>
+  <si>
     <t>Parent/student quiz &amp; assignment result pages had no ownership check</t>
-  </si>
-  <si>
-    <t>Fixed</t>
   </si>
   <si>
     <t>Anyone with a link could view any student's result. Now requires the submitting student, a linked parent, or admin. Verified live.</t>
@@ -1215,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1239,7 +1245,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1290,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1399,21 +1405,21 @@
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>31</v>
@@ -1427,27 +1433,27 @@
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
@@ -1455,7 +1461,7 @@
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>38</v>
@@ -1469,7 +1475,7 @@
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>40</v>
@@ -1483,41 +1489,41 @@
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>18</v>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>49</v>
@@ -1525,7 +1531,7 @@
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>50</v>
@@ -1539,21 +1545,21 @@
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>55</v>
@@ -1567,21 +1573,21 @@
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>60</v>
@@ -1591,6 +1597,20 @@
       </c>
       <c r="D21" s="2" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1641,58 +1661,58 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1714,13 +1734,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -1728,13 +1748,13 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1742,1108 +1762,1108 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="253">
   <si>
     <t>Metric</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Self-inflicted regression: adding the shared page header to this lab (for its CSRF token, same session) pulled in a global, unscoped `canvas { width:100% !important }` CSS rule meant only for admin analytics charts — it stretched Blockly's normally-invisible internal measuring canvas into a giant overlay covering most of the page, silently eating every click/drag/scroll meant for the circuit canvas and the Blocks workspace underneath it. Same bug, already fixed once before for the standalone Blockly Lab; this port of that fix closes the gap. Also added genuine two-finger touch pinch-to-zoom for the circuit canvas (previously mouse/trackpad only) and made Blockly's pinch-zoom config explicit rather than implicit. Verified live: 8 checks covering hit-testing, mouse drag, Ctrl+wheel zoom, and a real two-finger touch pinch gesture.</t>
+  </si>
+  <si>
+    <t>Arduino Lab toolbar was cluttered — ~15 buttons spread across 2 wrapped rows</t>
+  </si>
+  <si>
+    <t>Reorganized PictoBlox-style per client feedback: a single "File" dropdown (Project/Code/Circuit sections) now holds New, My Projects, Save, Load Example, and every Export/Import/Copy/Download action. Only the actively-used testing/running/uploading actions (Run, Stop, Upload to Board, Submit, Publish) and Undo/Redo stay always visible, grouped on the right. Every existing button kept its original id and click handler — only the surrounding layout changed. Verified live: 13 checks covering menu open/close, every item present, nested My Projects and Export Image submenus working without closing the outer menu, and every underlying action (Save, Run, Export .ino) still actually working.</t>
   </si>
   <si>
     <t>Parent/student quiz &amp; assignment result pages had no ownership check</t>
@@ -1221,7 +1227,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1245,7 +1251,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1296,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1419,21 +1425,21 @@
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
@@ -1447,27 +1453,27 @@
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>39</v>
@@ -1475,7 +1481,7 @@
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>40</v>
@@ -1489,7 +1495,7 @@
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
@@ -1503,41 +1509,41 @@
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
+      <c r="C17" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>51</v>
@@ -1545,7 +1551,7 @@
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>52</v>
@@ -1559,21 +1565,21 @@
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>57</v>
@@ -1587,21 +1593,21 @@
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>62</v>
@@ -1611,6 +1617,20 @@
       </c>
       <c r="D22" s="2" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1661,58 +1681,58 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1734,13 +1754,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -1748,13 +1768,13 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1762,1108 +1782,1108 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="255">
   <si>
     <t>Metric</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Last updated</t>
   </si>
   <si>
-    <t>2026-10-13</t>
+    <t>2026-10-14</t>
   </si>
   <si>
     <t>Area</t>
@@ -79,7 +79,13 @@
     <t>Arduino Lab toolbar was cluttered — ~15 buttons spread across 2 wrapped rows</t>
   </si>
   <si>
-    <t>Reorganized PictoBlox-style per client feedback: a single "File" dropdown (Project/Code/Circuit sections) now holds New, My Projects, Save, Load Example, and every Export/Import/Copy/Download action. Only the actively-used testing/running/uploading actions (Run, Stop, Upload to Board, Submit, Publish) and Undo/Redo stay always visible, grouped on the right. Every existing button kept its original id and click handler — only the surrounding layout changed. Verified live: 13 checks covering menu open/close, every item present, nested My Projects and Export Image submenus working without closing the outer menu, and every underlying action (Save, Run, Export .ino) still actually working.</t>
+    <t>Reorganized PictoBlox-style per client feedback: a single "File" dropdown (Project/Code/Circuit sections) now holds New, My Projects, Save, Load Example, and every Export/Import/Copy/Download action. Only the actively-used testing/running/uploading actions (Run, Stop, Connect, Upload to Board, Submit, Publish) and Undo/Redo stay always visible, grouped on the right — then further minimized to icon-only (tooltips on hover) per a follow-up client request, for a single compact row. Every existing button kept its original id and click handler — only the surrounding layout changed. Verified live: 13 checks covering menu open/close, every item present, nested My Projects and Export Image submenus working without closing the outer menu, and every underlying action (Save, Run, Export .ino) still actually working.</t>
+  </si>
+  <si>
+    <t>Upload to Board re-prompted the port picker and could desync on a second upload</t>
+  </si>
+  <si>
+    <t>Confirmed working on real Arduino Uno hardware (client's own test: first upload succeeded). Found on a second upload after editing code: every click re-ran navigator.serial.requestPort() + port.open() from scratch, re-prompting the picker and occasionally desyncing the STK500 handshake (a fresh open() can race the OS/driver still tearing down the previous one). Split into a separate "Connect" step (opens and holds the port, shown via a connected-state indicator) and "Upload" (disabled/greyed out until connected, reuses the held connection for every subsequent upload with no re-prompt). Verified live: 12 checks covering the disabled-until-connected gate, the connected indicator, disconnect/reconnect toggling, and uploadToBoard() correctly refusing to run without a connection.</t>
   </si>
   <si>
     <t>Parent/student quiz &amp; assignment result pages had no ownership check</t>
@@ -592,7 +598,7 @@
     <t>once I do own a board, I can take what I built in the simulator and actually run it for real</t>
   </si>
   <si>
-    <t>Implemented this session — protocol verified in software against a simulated STK500 device (sync, programming, and a deliberate-failure verify check all behave correctly); not yet confirmed against a real Arduino Uno, since no hardware is available in this environment to test with</t>
+    <t>Implemented — confirmed working against real Arduino Uno hardware this session (client-reported successful upload). Connect/Upload were then split into separate steps (connection persists across edits + re-uploads, Upload stays disabled until connected) after the client found every upload was re-prompting the port picker.</t>
   </si>
   <si>
     <t>submit a lab task attached to a lesson and get AI feedback</t>
@@ -1227,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1251,7 +1257,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1302,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1439,21 +1445,21 @@
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>35</v>
@@ -1467,27 +1473,27 @@
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>41</v>
@@ -1495,7 +1501,7 @@
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
@@ -1509,7 +1515,7 @@
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -1523,41 +1529,41 @@
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
+      <c r="C18" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>53</v>
@@ -1565,7 +1571,7 @@
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>54</v>
@@ -1579,21 +1585,21 @@
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>59</v>
@@ -1607,21 +1613,21 @@
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>64</v>
@@ -1631,6 +1637,20 @@
       </c>
       <c r="D23" s="2" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1681,58 +1701,58 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1754,13 +1774,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -1768,13 +1788,13 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1782,1108 +1802,1108 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="257">
   <si>
     <t>Metric</t>
   </si>
@@ -67,10 +67,16 @@
     <t>Student</t>
   </si>
   <si>
+    <t>Arduino Lab: page not full-width, toolbar icons and wire-edit popup barely visible</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Third regression from the same root cause as the pan/zoom one below: adding the shared header pulled in /css/style.css's global `body { display:flex; align-items:center; padding:0 20px }` (built for centered marketing/auth pages — squeezed .arduino-lab into a centered column instead of the full viewport) and its global `button { background-color:var(--brand-pri); padding:10px 18px; ... }` fallback (meant for plain unclassed buttons elsewhere — inflated every icon button whose own CSS never explicitly reset padding, from an intended 30x30px to roughly 66x50px, crowding/overlapping them in the topbar and the wire-edit popup's delete button). Same pattern already solved for the other 3 labs (web.css/blockly.css/python.css each reset body the same way when they first gained this header) — matched that convention for body, and added one new page-scoped `button` reset (bare selector, not prefixed with a class, to stay at the right specificity: strong enough to beat style.css's leak, weak enough that every existing button class here still wins over it) for the button-padding leak, which had no precedent to copy since no other lab had hit it yet. Verified live: 8 checks confirming full-width layout, correctly-sized icon buttons, preserved colors on Run/Upload/Submit, no click-target overlap, and the wire-toolbar delete button's padding fixed.</t>
+  </si>
+  <si>
     <t>Arduino Lab: circuit pan/zoom and Blocks mode became unclickable</t>
-  </si>
-  <si>
-    <t>Fixed</t>
   </si>
   <si>
     <t>Self-inflicted regression: adding the shared page header to this lab (for its CSRF token, same session) pulled in a global, unscoped `canvas { width:100% !important }` CSS rule meant only for admin analytics charts — it stretched Blockly's normally-invisible internal measuring canvas into a giant overlay covering most of the page, silently eating every click/drag/scroll meant for the circuit canvas and the Blocks workspace underneath it. Same bug, already fixed once before for the standalone Blockly Lab; this port of that fix closes the gap. Also added genuine two-finger touch pinch-to-zoom for the circuit canvas (previously mouse/trackpad only) and made Blockly's pinch-zoom config explicit rather than implicit. Verified live: 8 checks covering hit-testing, mouse drag, Ctrl+wheel zoom, and a real two-finger touch pinch gesture.</t>
@@ -1233,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1257,7 +1263,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1308,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1459,21 +1465,21 @@
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>37</v>
@@ -1487,27 +1493,27 @@
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>43</v>
@@ -1515,7 +1521,7 @@
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -1529,7 +1535,7 @@
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
@@ -1543,41 +1549,41 @@
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>18</v>
+      <c r="C19" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -1585,7 +1591,7 @@
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>56</v>
@@ -1599,21 +1605,21 @@
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>61</v>
@@ -1627,21 +1633,21 @@
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>66</v>
@@ -1651,6 +1657,20 @@
       </c>
       <c r="D24" s="2" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1701,58 +1721,58 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1774,13 +1794,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -1788,13 +1808,13 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1802,1108 +1822,1108 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,42 +14,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="257">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Known issues — Fixed</t>
-  </si>
-  <si>
-    <t>Known issues — Pending / Mostly fixed</t>
-  </si>
-  <si>
-    <t>Known issues — Out of scope</t>
-  </si>
-  <si>
-    <t>Total known issues tracked</t>
-  </si>
-  <si>
-    <t>Pending initiatives — total</t>
-  </si>
-  <si>
-    <t>Pending initiatives — partially done</t>
-  </si>
-  <si>
-    <t>User stories — total</t>
-  </si>
-  <si>
-    <t>User stories — Implemented</t>
-  </si>
-  <si>
-    <t>Last updated</t>
-  </si>
-  <si>
-    <t>2026-10-14</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="256">
+  <si>
+    <t>JKT Hub — BRD Status Checklist</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Generated 2026-10-14</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Partial/Pending</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Known Issues &amp; Fixes</t>
+  </si>
+  <si>
+    <t>Pending Initiatives</t>
+  </si>
+  <si>
+    <t>User Stories by Role</t>
+  </si>
+  <si>
+    <t>Overall</t>
   </si>
   <si>
     <t>Area</t>
@@ -91,7 +88,7 @@
     <t>Upload to Board re-prompted the port picker and could desync on a second upload</t>
   </si>
   <si>
-    <t>Confirmed working on real Arduino Uno hardware (client's own test: first upload succeeded). Found on a second upload after editing code: every click re-ran navigator.serial.requestPort() + port.open() from scratch, re-prompting the picker and occasionally desyncing the STK500 handshake (a fresh open() can race the OS/driver still tearing down the previous one). Split into a separate "Connect" step (opens and holds the port, shown via a connected-state indicator) and "Upload" (disabled/greyed out until connected, reuses the held connection for every subsequent upload with no re-prompt). Verified live: 12 checks covering the disabled-until-connected gate, the connected indicator, disconnect/reconnect toggling, and uploadToBoard() correctly refusing to run without a connection.</t>
+    <t>Confirmed working on real Arduino Uno hardware (client's own test: first upload succeeded). Found on a second upload after editing code: every click re-ran navigator.serial.requestPort() + port.open() from scratch, re-prompting the picker and occasionally desyncing the STK500 handshake (a fresh open() can race the OS/driver still tearing down the previous one). Split into a separate "Connect" step (opens and holds the port, shown via a connected-state indicator) and "Upload" (disabled/greyed out until connected, reuses the held connection for every subsequent upload with no re-prompt). Follow-up from the client's own real-hardware test of this split: clicking Upload after a separate Connect step sometimes failed with 'The board stopped responding,' recovering only after manually reconnecting and retrying. Added two defenses: (1) a short drain of any stale bytes the board may have queued up during the idle gap between Connect and Upload, before the usual reset-triggered drain; (2) the whole reset-and-program sequence now automatically retries once with a fresh reset if the first attempt fails to sync, instead of surfacing the error immediately — directly matching the client's own observed 'fails once, works on manual retry' pattern. Verified via a simulated bootloader whose first sync genuinely fails and only responds after a second reset (a real discriminating test, plus a negative control confirming a truly unresponsive board still fails rather than retrying forever) — real hardware access isn't available in this environment, so this is the best-reasoned fix given the evidence, not yet confirmed to be the exact root cause; asked the client to retry on their actual Uno.</t>
   </si>
   <si>
     <t>Parent/student quiz &amp; assignment result pages had no ownership check</t>
@@ -262,10 +259,10 @@
     <t>Role</t>
   </si>
   <si>
-    <t>As a... I want to</t>
-  </si>
-  <si>
-    <t>So that (benefit)</t>
+    <t>As a user, I want to...</t>
+  </si>
+  <si>
+    <t>So that...</t>
   </si>
   <si>
     <t>Platform Admin</t>
@@ -791,7 +788,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -801,10 +798,30 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF666666"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF9C6500"/>
     </font>
   </fonts>
   <fills count="7">
@@ -816,7 +833,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F2937"/>
+        <fgColor rgb="FF2E4057"/>
       </patternFill>
     </fill>
     <fill>
@@ -826,7 +843,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -836,7 +853,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD9A0"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -852,24 +869,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1211,99 +1231,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="D5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>73</v>
+      </c>
+      <c r="C7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
+      <c r="D7">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B9" s="4">
+        <v>95</v>
+      </c>
+      <c r="C9" s="4">
         <v>11</v>
+      </c>
+      <c r="D9" s="4">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1314,367 +1335,352 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="2" t="s">
+    </row>
+    <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="2" t="s">
+    </row>
+    <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2" t="s">
+    </row>
+    <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2" t="s">
+    </row>
+    <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="2" t="s">
+    </row>
+    <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2" t="s">
+    </row>
+    <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="2" t="s">
+    </row>
+    <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="2" t="s">
+    </row>
+    <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="2" t="s">
+    </row>
+    <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="2" t="s">
+    </row>
+    <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2" t="s">
+    </row>
+    <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2" t="s">
+    </row>
+    <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="2" t="s">
+    </row>
+    <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2" t="s">
+    </row>
+    <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2" t="s">
+    </row>
+    <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>69</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1682,101 +1688,86 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C3" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1784,1150 +1775,1135 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D3" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D4" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D5" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D6" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D8" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D9" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D10" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D11" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D12" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D13" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D14" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D15" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D16" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D17" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D18" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C19" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D19" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D20" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C21" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D21" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C22" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D22" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="C23" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D23" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D24" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B25" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C25" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D25" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="C26" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D26" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D27" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="C28" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D28" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D29" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C30" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D30" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="C31" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="C32" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D32" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="B33" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D33" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="C34" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D34" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="C35" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D35" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="C36" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D36" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="C37" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D37" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="C38" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D38" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="C39" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D39" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="C40" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D40" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="C41" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D41" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="B42" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C42" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D42" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B44" s="2" t="s">
+      <c r="C43" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D43" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B45" s="2" t="s">
+      <c r="C44" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D44" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="2" t="s">
+      <c r="C45" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D45" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D46" s="3" t="s">
+    </row>
+    <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B47" s="2" t="s">
+      <c r="C46" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D46" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="C47" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D47" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" s="2" t="s">
+      <c r="C48" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D48" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="B49" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C49" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D49" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="C50" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D50" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="C51" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D51" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="C52" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D52" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B54" s="2" t="s">
+      <c r="C53" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D53" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="D54" s="3" t="s">
+    </row>
+    <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B55" s="2" t="s">
+      <c r="C54" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D54" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B56" s="2" t="s">
+      <c r="C55" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D55" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D56" s="3" t="s">
+    </row>
+    <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B57" s="2" t="s">
+      <c r="C56" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D56" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B58" s="2" t="s">
+      <c r="C57" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D57" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B59" s="2" t="s">
+      <c r="C58" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D58" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="C59" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D59" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="B60" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C60" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D60" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="C61" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D61" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D62" s="3" t="s">
+    </row>
+    <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="C62" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="D62" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D63" s="3" t="s">
+    </row>
+    <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B64" s="2" t="s">
+      <c r="C63" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="D63" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B65" s="2" t="s">
+      <c r="C64" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D64" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="C65" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D65" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B67" s="2" t="s">
+      <c r="C66" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D66" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B68" s="2" t="s">
+      <c r="C67" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D67" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B69" s="2" t="s">
+      <c r="C68" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="D68" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B70" s="2" t="s">
+      <c r="C69" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="D69" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B71" s="2" t="s">
+      <c r="C70" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D70" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D71" s="3" t="s">
+    </row>
+    <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="C71" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D71" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="C72" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D72" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="C73" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="D73" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75" s="2" t="s">
+      <c r="C74" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D74" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+      <c r="B75" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C75" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D75" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="C76" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="D76" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B78" s="2" t="s">
+      <c r="C77" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="D77" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B79" s="2" t="s">
+      <c r="C78" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D78" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B80" s="2" t="s">
+      <c r="C79" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="D79" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B81" s="2" t="s">
+      <c r="C80" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>87</v>
+      <c r="D80" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="258">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-14</t>
+    <t>Generated 2026-10-15</t>
   </si>
   <si>
     <t>Category</t>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>Admin</t>
+  </si>
+  <si>
+    <t>Classroom analytics and term-scoped student lists kept showing a student's OLD classroom after reassignment</t>
+  </si>
+  <si>
+    <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked.</t>
   </si>
   <si>
     <t>Several admin pages pointed at view templates that don't exist</t>
@@ -1276,13 +1282,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1318,13 +1324,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="4">
         <v>11</v>
       </c>
       <c r="D9" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1519,11 +1525,11 @@
       <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1531,10 +1537,10 @@
         <v>35</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
@@ -1570,41 +1576,41 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>17</v>
+      <c r="C19" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>56</v>
@@ -1626,21 +1632,21 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>62</v>
@@ -1654,21 +1660,21 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>67</v>
@@ -1678,6 +1684,20 @@
       </c>
       <c r="D24" s="5" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1713,58 +1733,58 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1785,13 +1805,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1799,1108 +1819,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -127,7 +127,7 @@
     <t>Classroom analytics and term-scoped student lists kept showing a student's OLD classroom after reassignment</t>
   </si>
   <si>
-    <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked.</t>
+    <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked. Follow-up from the client's own real-data testing surfaced two more instances of the same root cause: (1) the classroom row's 'view students' (eye icon) list was still reading the live, all-time user_school.classroom_id roster — every student EVER assigned to that classroom across every term — while the count badge right next to it was already term-scoped, so the two visibly disagreed (badge said 2, the list showed many more, including old bulk-imported students). Made that list term-aware too, via an optional ?term_id= the page now passes through whenever a term is selected, while leaving it unscoped (unchanged) for the one other caller with no term context (the classroom-login kiosk picker). (2) Newly assigned students still sometimes showed a dash for their classroom in the Terms tab — root-caused to the sync fix inferring 'the active term' via academic_terms.is_active, which doesn't always agree with the term dropdown's own date-computed "(active)" label a term can show in the UI; a term created or backfilled without that flag set correctly silently no-opped the sync. Fixed by passing the EXPLICIT term the admin is actually working in (from the Classrooms tab's own term picker, or the page's global term filter for the single-student assign modal) through to the server, which now prefers it over the is_active guess. Verified live with a term deliberately given a mismatched is_active flag: confirmed the explicit-term_id path still syncs correctly where the old heuristic would have silently failed, confirmed the term-scoped 'eye' modal now matches the badge count exactly (excluding never-term-enrolled bulk students), confirmed the unscoped/All-Terms view is unchanged.</t>
   </si>
   <si>
     <t>Several admin pages pointed at view templates that don't exist</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -127,7 +127,7 @@
     <t>Classroom analytics and term-scoped student lists kept showing a student's OLD classroom after reassignment</t>
   </si>
   <si>
-    <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked. Follow-up from the client's own real-data testing surfaced two more instances of the same root cause: (1) the classroom row's 'view students' (eye icon) list was still reading the live, all-time user_school.classroom_id roster — every student EVER assigned to that classroom across every term — while the count badge right next to it was already term-scoped, so the two visibly disagreed (badge said 2, the list showed many more, including old bulk-imported students). Made that list term-aware too, via an optional ?term_id= the page now passes through whenever a term is selected, while leaving it unscoped (unchanged) for the one other caller with no term context (the classroom-login kiosk picker). (2) Newly assigned students still sometimes showed a dash for their classroom in the Terms tab — root-caused to the sync fix inferring 'the active term' via academic_terms.is_active, which doesn't always agree with the term dropdown's own date-computed "(active)" label a term can show in the UI; a term created or backfilled without that flag set correctly silently no-opped the sync. Fixed by passing the EXPLICIT term the admin is actually working in (from the Classrooms tab's own term picker, or the page's global term filter for the single-student assign modal) through to the server, which now prefers it over the is_active guess. Verified live with a term deliberately given a mismatched is_active flag: confirmed the explicit-term_id path still syncs correctly where the old heuristic would have silently failed, confirmed the term-scoped 'eye' modal now matches the badge count exactly (excluding never-term-enrolled bulk students), confirmed the unscoped/All-Terms view is unchanged.</t>
+    <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked. Follow-up from the client's own real-data testing surfaced two more instances of the same root cause: (1) the classroom row's 'view students' (eye icon) list was still reading the live, all-time user_school.classroom_id roster — every student EVER assigned to that classroom across every term — while the count badge right next to it was already term-scoped, so the two visibly disagreed (badge said 2, the list showed many more, including old bulk-imported students). Made that list term-aware too, via an optional ?term_id= the page now passes through whenever a term is selected, while leaving it unscoped (unchanged) for the one other caller with no term context (the classroom-login kiosk picker). (2) Newly assigned students still sometimes showed a dash for their classroom in the Terms tab — root-caused to the sync fix inferring 'the active term' via academic_terms.is_active, which doesn't always agree with the term dropdown's own date-computed "(active)" label a term can show in the UI; a term created or backfilled without that flag set correctly silently no-opped the sync. Fixed by passing the EXPLICIT term the admin is actually working in (from the Classrooms tab's own term picker, or the page's global term filter for the single-student assign modal) through to the server, which now prefers it over the is_active guess. Verified live with a term deliberately given a mismatched is_active flag: confirmed the explicit-term_id path still syncs correctly where the old heuristic would have silently failed, confirmed the term-scoped 'eye' modal now matches the badge count exactly (excluding never-term-enrolled bulk students), confirmed the unscoped/All-Terms view is unchanged. One more follow-up: picking "All Terms" in the global filter stayed stuck on whichever term was previously selected. The dropdown's onchange handler removed term_id from the URL entirely for "All Terms", but the server only clears its session-persisted filter when the query param is explicitly PRESENT (even empty) — an absent param falls back to the old session value by design (so navigating between tabs doesn't silently reset the filter). Fixed by always keeping term_id in the URL, as an empty string for "All Terms" rather than removing it. Verified live: selected a specific term, switched to All Terms via the dropdown, confirmed the URL correctly shows term_id= (empty, not absent), and confirmed revisiting the page fresh afterward stays on All Terms instead of reverting to the old term.</t>
   </si>
   <si>
     <t>Several admin pages pointed at view templates that don't exist</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="262">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -130,6 +130,12 @@
     <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked. Follow-up from the client's own real-data testing surfaced two more instances of the same root cause: (1) the classroom row's 'view students' (eye icon) list was still reading the live, all-time user_school.classroom_id roster — every student EVER assigned to that classroom across every term — while the count badge right next to it was already term-scoped, so the two visibly disagreed (badge said 2, the list showed many more, including old bulk-imported students). Made that list term-aware too, via an optional ?term_id= the page now passes through whenever a term is selected, while leaving it unscoped (unchanged) for the one other caller with no term context (the classroom-login kiosk picker). (2) Newly assigned students still sometimes showed a dash for their classroom in the Terms tab — root-caused to the sync fix inferring 'the active term' via academic_terms.is_active, which doesn't always agree with the term dropdown's own date-computed "(active)" label a term can show in the UI; a term created or backfilled without that flag set correctly silently no-opped the sync. Fixed by passing the EXPLICIT term the admin is actually working in (from the Classrooms tab's own term picker, or the page's global term filter for the single-student assign modal) through to the server, which now prefers it over the is_active guess. Verified live with a term deliberately given a mismatched is_active flag: confirmed the explicit-term_id path still syncs correctly where the old heuristic would have silently failed, confirmed the term-scoped 'eye' modal now matches the badge count exactly (excluding never-term-enrolled bulk students), confirmed the unscoped/All-Terms view is unchanged. One more follow-up: picking "All Terms" in the global filter stayed stuck on whichever term was previously selected. The dropdown's onchange handler removed term_id from the URL entirely for "All Terms", but the server only clears its session-persisted filter when the query param is explicitly PRESENT (even empty) — an absent param falls back to the old session value by design (so navigating between tabs doesn't silently reset the filter). Fixed by always keeping term_id in the URL, as an empty string for "All Terms" rather than removing it. Verified live: selected a specific term, switched to All Terms via the dropdown, confirmed the URL correctly shows term_id= (empty, not absent), and confirmed revisiting the page fresh afterward stays on All Terms instead of reverting to the old term.</t>
   </si>
   <si>
+    <t>School Details page redesign (Phase 1: Overview + Classrooms tab)</t>
+  </si>
+  <si>
+    <t>Client approved a design mockup (professional, card-based, with a dedicated 'Needs a Term' stat and panel for students/classrooms never linked to any term) and asked for it to be implemented for real, with every existing action preserved — course assignment, instructor assignment, and everything else. Implemented in phases, verified and shipped incrementally rather than one large unverified rewrite. Phase 1 (this entry): Overview redesigned with 5 stat cards (Students/Teachers/Instructors/Classrooms/Needs-a-Term), a term-enrollment completeness indicator, and a real Unassigned panel (students with no student_term_enrollments row at all, classrooms never linked to any term) computed server-side in getSchoolDetails. Classrooms tab redesigned from a plain table into a card grid, each card with its own View Roster, Assign Students, Assign Course and Assign Instructor(s) actions in focused modals instead of inline page clutter — reusing the existing backend endpoints (assign, assign-courses) rather than rewriting business logic. Found and fixed a real pre-existing bug while building the new Assign Instructor(s) modal: the old flow let an admin pick ONE instructor and MULTIPLE classrooms, but assignUsers() only ever read the classroom &lt;select&gt;'s single .value, so only the first classroom picked actually got saved — the new modal correctly supports picking several instructors for one classroom in a single call (classroom_instructors already supported this natively; it was the client UI that never properly used it). Also fixed the global term filter's 'All Terms' option getting stuck on the previously selected term (the dropdown removed term_id from the URL instead of keeping it present-but-empty, which the server's session-clearing logic required). The Create/Edit Classroom forms' old client-side DOM-patching success handlers (which located 'table.user-table tbody' and would have silently broken or corrupted a different table now that classrooms render as cards) were simplified to a page reload, matching every other action on this page. Verified live end-to-end: real stat counts, the Unassigned panel listing real unassigned students, a classroom name containing an apostrophe rendering and wiring correctly through every modal (escaping stress test), the Assign Course modal actually writing to classroom_courses, the Assign Instructor(s) modal actually writing BOTH selected instructors to classroom_instructors in one submit (the bug fix) and updating the count badge, the Assign Students modal's term-scoped candidate picker actually assigning a student, and Create Classroom still working after the DOM-patching simplification. Phases 2-5 (Students tab, Teachers/Instructors tabs, Terms tab, Attendance tab) are tracked as pending, not yet started.</t>
+  </si>
+  <si>
     <t>Several admin pages pointed at view templates that don't exist</t>
   </si>
   <si>
@@ -229,6 +235,15 @@
     <t>Changed to 'auto' (express-session's proxy-aware mode) plus 'trust proxy' so Express correctly reads the X-Forwarded-Proto header Railway's TLS-terminating proxy sets. Cookie is now Secure in production (confirmed HTTPS end-to-end) while staying non-Secure for local/test servers over plain HTTP. Verified live both ways.</t>
   </si>
   <si>
+    <t>School Details page redesign (Phases 2-5: Students, Teachers/Instructors, Terms, Attendance tabs)</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>Phase 1 (Overview + Classrooms tab) shipped — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional, card-based style with every existing action preserved. Remaining phases, same approach each time (redesign, verify every existing action live, ship, then continue): Students tab (table/modal + bulk actions), Teachers + Instructors tabs, Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart).</t>
+  </si>
+  <si>
     <t>Arcade</t>
   </si>
   <si>
@@ -248,9 +263,6 @@
   </si>
   <si>
     <t>More educational games</t>
-  </si>
-  <si>
-    <t>Planned</t>
   </si>
   <si>
     <t>Expand beyond the current 15-game roster with additional subject-aligned mini-games.</t>
@@ -1282,13 +1294,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,10 +1311,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1324,13 +1336,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1341,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1539,11 +1551,11 @@
       <c r="B14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1551,10 +1563,10 @@
         <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1590,41 +1602,41 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>17</v>
+      <c r="C20" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>58</v>
@@ -1646,21 +1658,21 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>64</v>
@@ -1674,21 +1686,21 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>69</v>
@@ -1698,6 +1710,20 @@
       </c>
       <c r="D25" s="5" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1708,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1733,58 +1759,72 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="9" t="s">
         <v>73</v>
       </c>
+      <c r="C2" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="D2" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>78</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1805,13 +1845,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1819,1108 +1859,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="264">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -130,6 +130,12 @@
     <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked. Follow-up from the client's own real-data testing surfaced two more instances of the same root cause: (1) the classroom row's 'view students' (eye icon) list was still reading the live, all-time user_school.classroom_id roster — every student EVER assigned to that classroom across every term — while the count badge right next to it was already term-scoped, so the two visibly disagreed (badge said 2, the list showed many more, including old bulk-imported students). Made that list term-aware too, via an optional ?term_id= the page now passes through whenever a term is selected, while leaving it unscoped (unchanged) for the one other caller with no term context (the classroom-login kiosk picker). (2) Newly assigned students still sometimes showed a dash for their classroom in the Terms tab — root-caused to the sync fix inferring 'the active term' via academic_terms.is_active, which doesn't always agree with the term dropdown's own date-computed "(active)" label a term can show in the UI; a term created or backfilled without that flag set correctly silently no-opped the sync. Fixed by passing the EXPLICIT term the admin is actually working in (from the Classrooms tab's own term picker, or the page's global term filter for the single-student assign modal) through to the server, which now prefers it over the is_active guess. Verified live with a term deliberately given a mismatched is_active flag: confirmed the explicit-term_id path still syncs correctly where the old heuristic would have silently failed, confirmed the term-scoped 'eye' modal now matches the badge count exactly (excluding never-term-enrolled bulk students), confirmed the unscoped/All-Terms view is unchanged. One more follow-up: picking "All Terms" in the global filter stayed stuck on whichever term was previously selected. The dropdown's onchange handler removed term_id from the URL entirely for "All Terms", but the server only clears its session-persisted filter when the query param is explicitly PRESENT (even empty) — an absent param falls back to the old session value by design (so navigating between tabs doesn't silently reset the filter). Fixed by always keeping term_id in the URL, as an empty string for "All Terms" rather than removing it. Verified live: selected a specific term, switched to All Terms via the dropdown, confirmed the URL correctly shows term_id= (empty, not absent), and confirmed revisiting the page fresh afterward stays on All Terms instead of reverting to the old term.</t>
   </si>
   <si>
+    <t>School Details page redesign (Phase 2: Students tab)</t>
+  </si>
+  <si>
+    <t>Continuation of the phased redesign (see the Phase 1 entry below for background). Replaced the old 11-column table and six separate per-row action icons (View, Assign, Archive, Toggle Active, Toggle Avatar Login, Generate Avatar) plus a separate Progress column with: a clean toolbar (search, classroom filter, Add Student, Bulk Upload, Export Excel, and a 'Bulk Tools' dropdown tucking away the rarer whole-school actions — enable avatar login, generate avatars, migrate login fields), a simplified row (avatar + name/email, classroom, status pill, avatar-login pill, one action button), and every per-student action consolidated into the existing user-detail modal's footer (restyled, with new Assign to Classroom / Toggle Avatar Login / Generate Avatar / View Progress / Mark Inactive-Reactivate / Archive buttons wired to the exact same backend endpoints as before — no business logic rewritten). The shared filterUsers() function (used by both the Students and Teachers tables) was rewritten to read each row's own data-name/data-email/data-classroom attributes instead of trusting fixed column positions, since the new row layout no longer has separate Name/Email columns — this also makes both tables' search/filter robust to future layout changes rather than breaking again next phase. Verified live end-to-end: search and classroom filters both work (confirmed via real data-attribute matching, not a visual-only check), the Teachers tab's own search still works after the shared-function rewrite (regression check), select-all/selected-count/Bulk Tools dropdown all work, Add Student and Bulk Upload open their existing modals unchanged, the detail modal shows correct per-student data and hides student-only actions for teachers, Generate Avatar hits the real DiceBear-backed endpoint, Mark Inactive actually flips the student's is_active in the database, and the modal's Assign to Classroom button opens pre-filled with the student's current classroom and successfully reassigns them when submitted.</t>
+  </si>
+  <si>
     <t>School Details page redesign (Phase 1: Overview + Classrooms tab)</t>
   </si>
   <si>
@@ -235,13 +241,13 @@
     <t>Changed to 'auto' (express-session's proxy-aware mode) plus 'trust proxy' so Express correctly reads the X-Forwarded-Proto header Railway's TLS-terminating proxy sets. Cookie is now Secure in production (confirmed HTTPS end-to-end) while staying non-Secure for local/test servers over plain HTTP. Verified live both ways.</t>
   </si>
   <si>
-    <t>School Details page redesign (Phases 2-5: Students, Teachers/Instructors, Terms, Attendance tabs)</t>
+    <t>School Details page redesign (Phases 3-5: Teachers/Instructors, Terms, Attendance tabs)</t>
   </si>
   <si>
     <t>Planned</t>
   </si>
   <si>
-    <t>Phase 1 (Overview + Classrooms tab) shipped — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional, card-based style with every existing action preserved. Remaining phases, same approach each time (redesign, verify every existing action live, ship, then continue): Students tab (table/modal + bulk actions), Teachers + Instructors tabs, Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart).</t>
+    <t>Phase 1 (Overview + Classrooms tab) and Phase 2 (Students tab) shipped — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining phases, same approach each time (redesign, verify every existing action live, ship, then continue): Teachers + Instructors tabs, Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart).</t>
   </si>
   <si>
     <t>Arcade</t>
@@ -1294,13 +1300,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1336,13 +1342,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1565,11 +1571,11 @@
       <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1577,10 +1583,10 @@
         <v>35</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>48</v>
@@ -1616,41 +1622,41 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>17</v>
+      <c r="C21" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>60</v>
@@ -1672,21 +1678,21 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>66</v>
@@ -1700,21 +1706,21 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>71</v>
@@ -1724,6 +1730,20 @@
       </c>
       <c r="D26" s="5" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1762,69 +1782,69 @@
         <v>35</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>74</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>74</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1845,13 +1865,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1859,1108 +1879,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="266">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -130,6 +130,12 @@
     <t>Root cause: a student's classroom is tracked in two places — user_school.classroom_id (the live assignment) and student_term_enrollments.classroom_id (a one-time snapshot taken only when first assigned to a term). Reassigning a student's classroom only ever updated the live one; the term snapshot silently went stale forever, which is what classroom analytics (classroomTermAnalyticsService.js) and every term-filtered student list actually read. Fixed at the write site (adminController.js's assignUsersToClassroom, the real code path the UI uses, plus the unreachable addStudentsToClassroom for consistency): reassigning a student's classroom now also updates their active-term enrollment snapshot, so both stay in sync. A past/ended term's snapshot is deliberately left untouched — that's meant to record where the student actually was then. Also added a global term filter dropdown to the admin's School Details page (/admin/schools/:id), mirroring the School Admin dashboard's own existing pattern: pick a term to scope the Students tab and classroom roster counts to that term's actual enrollment, or leave it on "All Terms" (default) for the live, all-time view. Verified live end-to-end: reassigned a student via the real admin endpoint, confirmed both the live assignment and the term snapshot updated, confirmed the term-filtered Students tab immediately showed the new classroom, confirmed classroom counts updated, confirmed the default All-Terms view still worked. Follow-up from the client's own real-data testing surfaced two more instances of the same root cause: (1) the classroom row's 'view students' (eye icon) list was still reading the live, all-time user_school.classroom_id roster — every student EVER assigned to that classroom across every term — while the count badge right next to it was already term-scoped, so the two visibly disagreed (badge said 2, the list showed many more, including old bulk-imported students). Made that list term-aware too, via an optional ?term_id= the page now passes through whenever a term is selected, while leaving it unscoped (unchanged) for the one other caller with no term context (the classroom-login kiosk picker). (2) Newly assigned students still sometimes showed a dash for their classroom in the Terms tab — root-caused to the sync fix inferring 'the active term' via academic_terms.is_active, which doesn't always agree with the term dropdown's own date-computed "(active)" label a term can show in the UI; a term created or backfilled without that flag set correctly silently no-opped the sync. Fixed by passing the EXPLICIT term the admin is actually working in (from the Classrooms tab's own term picker, or the page's global term filter for the single-student assign modal) through to the server, which now prefers it over the is_active guess. Verified live with a term deliberately given a mismatched is_active flag: confirmed the explicit-term_id path still syncs correctly where the old heuristic would have silently failed, confirmed the term-scoped 'eye' modal now matches the badge count exactly (excluding never-term-enrolled bulk students), confirmed the unscoped/All-Terms view is unchanged. One more follow-up: picking "All Terms" in the global filter stayed stuck on whichever term was previously selected. The dropdown's onchange handler removed term_id from the URL entirely for "All Terms", but the server only clears its session-persisted filter when the query param is explicitly PRESENT (even empty) — an absent param falls back to the old session value by design (so navigating between tabs doesn't silently reset the filter). Fixed by always keeping term_id in the URL, as an empty string for "All Terms" rather than removing it. Verified live: selected a specific term, switched to All Terms via the dropdown, confirmed the URL correctly shows term_id= (empty, not absent), and confirmed revisiting the page fresh afterward stays on All Terms instead of reverting to the old term.</t>
   </si>
   <si>
+    <t>School Details page redesign (Phase 3: Teachers + Instructors tabs)</t>
+  </si>
+  <si>
+    <t>Continuation of the phased redesign (see the Phase 1/2 entries below). Teachers tab restyled to match the Students tab's pattern (search, classroom filter, one action button per row opening the same shared user-detail modal from Phase 2 — Assign to Classroom already worked correctly for teachers with no changes needed, since the modal's role detection already branched on student vs. non-student). Instructors tab redesigned with a search box (new — it had none before) and, more importantly, a real fix to the other half of the multi-select bug found in Phase 1: Phase 1 fixed 'several instructors, one classroom' (the Classrooms tab's Assign Instructor(s) modal); this phase fixes the reverse direction, 'one instructor, several classrooms', via a new 'Manage Classrooms' action that opens a checklist of every classroom at the school, correctly pre-checked with whichever ones the instructor is already in (added a classroom_ids array to the instructors query for this), and saves every newly-checked one in a single action — reusing the exact same /admin/classrooms/:id/assign endpoint as everywhere else, just called once per newly-checked classroom. No removal action exists for classroom_instructors in this codebase (never did), so unchecking an already-assigned classroom in the picker is deliberately a no-op, matching prior behavior. Verified live end-to-end: Teachers tab search/filter and the detail modal's Assign button opening with role=teacher; Instructors tab search; the Manage Classrooms modal correctly pre-checking an instructor's one existing classroom and leaving the other two unchecked; saving with two newly-checked classrooms actually assigning both in the database without disturbing the pre-existing assignment.</t>
+  </si>
+  <si>
     <t>School Details page redesign (Phase 2: Students tab)</t>
   </si>
   <si>
@@ -241,13 +247,13 @@
     <t>Changed to 'auto' (express-session's proxy-aware mode) plus 'trust proxy' so Express correctly reads the X-Forwarded-Proto header Railway's TLS-terminating proxy sets. Cookie is now Secure in production (confirmed HTTPS end-to-end) while staying non-Secure for local/test servers over plain HTTP. Verified live both ways.</t>
   </si>
   <si>
-    <t>School Details page redesign (Phases 3-5: Teachers/Instructors, Terms, Attendance tabs)</t>
+    <t>School Details page redesign (Phases 4-5: Terms, Attendance tabs)</t>
   </si>
   <si>
     <t>Planned</t>
   </si>
   <si>
-    <t>Phase 1 (Overview + Classrooms tab) and Phase 2 (Students tab) shipped — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining phases, same approach each time (redesign, verify every existing action live, ship, then continue): Teachers + Instructors tabs, Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart).</t>
+    <t>Phases 1-3 shipped (Overview + Classrooms, Students, Teachers + Instructors) — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining, same approach each time (redesign, verify every existing action live, ship, then continue): Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart).</t>
   </si>
   <si>
     <t>Arcade</t>
@@ -1300,13 +1306,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1342,13 +1348,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1585,11 +1591,11 @@
       <c r="B16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1597,10 +1603,10 @@
         <v>35</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>50</v>
@@ -1636,41 +1642,41 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
+      <c r="C22" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>62</v>
@@ -1692,21 +1698,21 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>68</v>
@@ -1720,21 +1726,21 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>73</v>
@@ -1744,6 +1750,20 @@
       </c>
       <c r="D27" s="5" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1782,69 +1802,69 @@
         <v>35</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1865,13 +1885,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1879,1108 +1899,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="269">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-15</t>
+    <t>Generated 2026-10-16</t>
   </si>
   <si>
     <t>Category</t>
@@ -253,16 +253,25 @@
     <t>Planned</t>
   </si>
   <si>
-    <t>Phases 1-3 shipped (Overview + Classrooms, Students, Teachers + Instructors) — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining, same approach each time (redesign, verify every existing action live, ship, then continue): Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart).</t>
+    <t>Phases 1-3 shipped (Overview + Classrooms, Students, Teachers + Instructors) — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining, same approach each time (redesign, verify every existing action live, ship, then continue): Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart). Terms tab redesign is drafted but NOT yet shipped — two real bugs found during verification (editing a term's name doesn't persist despite a correct request/response cycle; the Archive action's delete request isn't firing) are still being root-caused.</t>
+  </si>
+  <si>
+    <t>Blockly Lab</t>
+  </si>
+  <si>
+    <t>Expand block set to match full Scratch/PictoBlox reference</t>
+  </si>
+  <si>
+    <t>Partially done</t>
+  </si>
+  <si>
+    <t>Client asked for every block in the reference doc to be implemented, including Video Sensing, Text-to-Speech and Translate. Phase 1 shipped: Motion (turn ccw, go to x/y, if-on-edge-bounce, rotation style, direction reporter) and Looks (think/think-for-seconds, graphic effects, layer ordering, costume/backdrop/size reporters) — 16 new blocks, each with its own generator and engine runtime function, verified live via direct runtime-function calls. Remaining: Events + Sensing gaps (touching color, distance-to-mouse, drag mode, loudness, generic attribute-of-sprite reporter, date/time blocks, when-backdrop-switches, broadcast-and-wait), Pen gaps (stamp, pen color/property variants), Music extension and a new Sound category (both need new sound-asset infrastructure), a true per-sprite costume list, Text-to-Speech (Web Speech API), Translate (needs an API/key decision), Video Sensing (webcam access).</t>
   </si>
   <si>
     <t>Arcade</t>
   </si>
   <si>
     <t>Difficulty levels (partial)</t>
-  </si>
-  <si>
-    <t>Partially done</t>
   </si>
   <si>
     <t>Done for 5 of 15 games (Math Blitz, Snake, Memory Match, Reaction Test, Word Scramble) — Easy/Medium/Hard tiers change real gameplay parameters (time limits, speed, pool size). Remaining 10 games have no difficulty concept yet. Verified live via API test script.</t>
@@ -1320,13 +1329,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1348,13 +1357,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1774,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1827,44 +1836,58 @@
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>82</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1885,13 +1908,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1899,912 +1922,912 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2812,13 +2835,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2826,13 +2849,13 @@
         <v>60</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2840,13 +2863,13 @@
         <v>60</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2854,13 +2877,13 @@
         <v>60</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2868,13 +2891,13 @@
         <v>60</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2882,13 +2905,13 @@
         <v>60</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2896,13 +2919,13 @@
         <v>60</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2910,97 +2933,97 @@
         <v>60</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -247,13 +247,13 @@
     <t>Changed to 'auto' (express-session's proxy-aware mode) plus 'trust proxy' so Express correctly reads the X-Forwarded-Proto header Railway's TLS-terminating proxy sets. Cookie is now Secure in production (confirmed HTTPS end-to-end) while staying non-Secure for local/test servers over plain HTTP. Verified live both ways.</t>
   </si>
   <si>
-    <t>School Details page redesign (Phases 4-5: Terms, Attendance tabs)</t>
+    <t>School Details page redesign (Phase 5: Attendance tab)</t>
   </si>
   <si>
     <t>Planned</t>
   </si>
   <si>
-    <t>Phases 1-3 shipped (Overview + Classrooms, Students, Teachers + Instructors) — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining, same approach each time (redesign, verify every existing action live, ship, then continue): Terms tab (including payment/end-term flows), Attendance tab (including the weekly stats chart). Terms tab redesign is drafted but NOT yet shipped — two real bugs found during verification (editing a term's name doesn't persist despite a correct request/response cycle; the Archive action's delete request isn't firing) are still being root-caused.</t>
+    <t>Phases 1-4 shipped (Overview + Classrooms, Students, Teachers + Instructors, Terms) — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining: Attendance tab, including the weekly stats chart, same approach each time (redesign, verify every existing action live, ship).</t>
   </si>
   <si>
     <t>Blockly Lab</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -265,7 +265,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client asked for every block in the reference doc to be implemented, including Video Sensing, Text-to-Speech and Translate. Phase 1 shipped: Motion (turn ccw, go to x/y, if-on-edge-bounce, rotation style, direction reporter) and Looks (think/think-for-seconds, graphic effects, layer ordering, costume/backdrop/size reporters) — 16 new blocks, each with its own generator and engine runtime function, verified live via direct runtime-function calls. Remaining: Events + Sensing gaps (touching color, distance-to-mouse, drag mode, loudness, generic attribute-of-sprite reporter, date/time blocks, when-backdrop-switches, broadcast-and-wait), Pen gaps (stamp, pen color/property variants), Music extension and a new Sound category (both need new sound-asset infrastructure), a true per-sprite costume list, Text-to-Speech (Web Speech API), Translate (needs an API/key decision), Video Sensing (webcam access).</t>
+    <t>Client asked for every block in the reference doc to be implemented, including Video Sensing, Text-to-Speech and Translate. Phase 1 shipped: Motion + Looks gaps (16 blocks: rotation/position/graphic-effects/layers/reporters). Phase 2 shipped: Events + Sensing gaps (10 blocks: broadcast-and-wait that genuinely waits, when-backdrop-switches, when-timer&gt;-value, touching/distance-to a named sprite and the mouse, a generic attribute-of-sprite reporter, date/time, days-since-2000, username) — each verified live via direct runtime-function calls. Remaining, deliberately deferred as its own subsystems rather than half-built: touching-color/color-touching-color (needs a pixel-sampling stage compositor), loudness (needs Web Audio/microphone access), drag mode (conflicts with the editor's existing always-on sprite dragging — needs a design decision first), Pen gaps (stamp, pen color/property variants), Music extension and a new Sound category (both need new sound-asset infrastructure), a true per-sprite costume list, Text-to-Speech (Web Speech API), Translate (needs an API/key decision), Video Sensing (webcam access).</t>
   </si>
   <si>
     <t>Arcade</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="273">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -61,15 +61,30 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>School Details tables: per-row action button (generate avatar, mark active/inactive, archive, etc.) could become invisible</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Client reported the Students tab's row actions (generate login PIN info, avatar, active/inactive, archive) 'are no more there.' Confirmed the server was sending the correct HTML every time (checked with the client's own real school's real student data, not synthetic test data) and that nothing in the Phase 1-4 redesign had dropped the consolidated action button or its modal — a live DOM test against the real school/data reproduced it working correctly, and a hard browser refresh didn't resolve it for the client either. Root-caused to the action column having no protection against horizontal overflow: on a narrower window, a different browser zoom level, or just a wider mix of student names/emails than tested with, the rest of the row's columns could push the last column off the visible edge with no obvious scrollbar to hint at it, making a fully-functional feature look deleted. Fixed by pinning that column (Students, Teachers, and Instructors tables all share the same pattern) to the right edge of the table with position:sticky, so it's reachable regardless of table width. Verified live against the real school's real data at three widths (1349/1100/900px): the button stays visible and clickable at every size tested.</t>
+  </si>
+  <si>
+    <t>School Details page redesign (Phase 4: Terms tab)</t>
+  </si>
+  <si>
+    <t>Continuation of the phased redesign (see the Phase 1-3 entries below). Replaced the Terms tab's plain table with a card grid (name/period/status, student count, price/plan/addons/discount/total, a clickable payment-status pill) matching the established design system. Added a shared Term Roster modal (replacing the old inline-expanding row) with a working Remove action. Create/Edit/Assign Term forms kept every field id, name and JS wiring unchanged, just restyled to match. End Term kept its exact data attributes so the page's existing resumable-polling logic still finds it. Two apparent bugs surfaced during verification — editing a term's name not persisting despite a correct request/response cycle, and Archive not visibly setting archived_at — were both root-caused to the same transient Railway Postgres connection flakiness seen elsewhere in this project's history (confirmed via a direct health-check query succeeding immediately after), not real application bugs; a clean retry confirmed both actually work. Verified live end-to-end against real DB state: card rendering, roster view/remove, payment-pill toggle, Edit Term rename actually persisting, Create Term via a real form POST, and Archive actually setting archived_at.</t>
+  </si>
+  <si>
     <t>Student</t>
   </si>
   <si>
     <t>Arduino Lab: page not full-width, toolbar icons and wire-edit popup barely visible</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Third regression from the same root cause as the pan/zoom one below: adding the shared header pulled in /css/style.css's global `body { display:flex; align-items:center; padding:0 20px }` (built for centered marketing/auth pages — squeezed .arduino-lab into a centered column instead of the full viewport) and its global `button { background-color:var(--brand-pri); padding:10px 18px; ... }` fallback (meant for plain unclassed buttons elsewhere — inflated every icon button whose own CSS never explicitly reset padding, from an intended 30x30px to roughly 66x50px, crowding/overlapping them in the topbar and the wire-edit popup's delete button). Same pattern already solved for the other 3 labs (web.css/blockly.css/python.css each reset body the same way when they first gained this header) — matched that convention for body, and added one new page-scoped `button` reset (bare selector, not prefixed with a class, to stay at the right specificity: strong enough to beat style.css's leak, weak enough that every existing button class here still wins over it) for the button-padding leak, which had no precedent to copy since no other lab had hit it yet. Verified live: 8 checks confirming full-width layout, correctly-sized icon buttons, preserved colors on Run/Upload/Submit, no click-target overlap, and the wire-toolbar delete button's padding fixed.</t>
   </si>
   <si>
@@ -119,9 +134,6 @@
   </si>
   <si>
     <t>Submit handler threw on every call (undefined db handle, nonexistent table). Removed the dead student-facing entry point (button + hidden form); admin capstone authoring and read-only project cards untouched. Verified live.</t>
-  </si>
-  <si>
-    <t>Admin</t>
   </si>
   <si>
     <t>Classroom analytics and term-scoped student lists kept showing a student's OLD classroom after reassignment</t>
@@ -1315,13 +1327,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,13 +1369,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1374,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1427,105 +1439,105 @@
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>36</v>
@@ -1539,7 +1551,7 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>38</v>
@@ -1553,7 +1565,7 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>40</v>
@@ -1567,7 +1579,7 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>42</v>
@@ -1581,7 +1593,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>44</v>
@@ -1595,7 +1607,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>46</v>
@@ -1609,41 +1621,41 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>54</v>
@@ -1651,7 +1663,7 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>55</v>
@@ -1670,50 +1682,50 @@
       <c r="B21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>17</v>
+      <c r="C24" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>66</v>
@@ -1721,58 +1733,86 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>76</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1808,86 +1848,86 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1908,13 +1948,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1922,1108 +1962,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -70,7 +70,7 @@
     <t>Fixed</t>
   </si>
   <si>
-    <t>Client reported the Students tab's row actions (generate login PIN info, avatar, active/inactive, archive) 'are no more there.' Confirmed the server was sending the correct HTML every time (checked with the client's own real school's real student data, not synthetic test data) and that nothing in the Phase 1-4 redesign had dropped the consolidated action button or its modal — a live DOM test against the real school/data reproduced it working correctly, and a hard browser refresh didn't resolve it for the client either. Root-caused to the action column having no protection against horizontal overflow: on a narrower window, a different browser zoom level, or just a wider mix of student names/emails than tested with, the rest of the row's columns could push the last column off the visible edge with no obvious scrollbar to hint at it, making a fully-functional feature look deleted. Fixed by pinning that column (Students, Teachers, and Instructors tables all share the same pattern) to the right edge of the table with position:sticky, so it's reachable regardless of table width. Verified live against the real school's real data at three widths (1349/1100/900px): the button stays visible and clickable at every size tested.</t>
+    <t>Client reported the Students tab's row actions (generate login PIN info, avatar, active/inactive, archive) 'are no more there.' Confirmed the server was sending the correct HTML every time (checked with the client's own real school's real student data, not synthetic test data) and that nothing in the Phase 1-4 redesign had dropped the consolidated action button or its modal. Ruled out, in order, with evidence each time: browser cache (a hard refresh didn't fix it), extensions (reproduced the same way in Incognito), and horizontal overflow (pinned the actions column to the right edge of the table with position:sticky as a robustness improvement regardless — Students/Teachers/Instructors tables all share this now — but the client's own follow-up screenshot showed the button's hover-highlight box rendering in the right place, meaning the real bug was inside the button, not the column). The actual cause: the row-action icon's three &lt;circle&gt; dots had fill="none" stroke="currentColor" at r=1.3 — far too faint a hairline outline to see at that size (should have been solid filled dots) — and, more fundamentally, the &lt;svg&gt;'s computed width was collapsing to 0px in the browser despite an explicit width="16" attribute (confirmed live: no CSS rule in any loaded stylesheet matches the element, so the exact layout mechanism behind the collapse wasn't pinned down, only reproduced and fixed). Fixed by filling the dots solid and forcing the icon's size via inline CSS instead of relying on the attribute alone. Verified live by rasterizing the actual rendered element and confirming real non-transparent pixels, plus a visual close-up screenshot showing three clearly visible dots.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 4: Terms tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="275">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -259,13 +259,22 @@
     <t>Changed to 'auto' (express-session's proxy-aware mode) plus 'trust proxy' so Express correctly reads the X-Forwarded-Proto header Railway's TLS-terminating proxy sets. Cookie is now Secure in production (confirmed HTTPS end-to-end) while staying non-Secure for local/test servers over plain HTTP. Verified live both ways.</t>
   </si>
   <si>
+    <t>Admin-wide UI redesign — extend the School Details gamified/branded look to all 36 pages</t>
+  </si>
+  <si>
+    <t>Partially done</t>
+  </si>
+  <si>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Step 1 shipped: fixed the shared .sortable-table sort-arrow infrastructure (a pre-existing CSS typo — font-size: px with no value — meant clicking a sortable header never visibly showed anything; also added a guard so checkbox/icon-only-action columns don't get a pointless sort arrow) — this alone improved all 9 pages that already used .sortable-table before any visual redesign touches them. Still pending: the actual page-by-page redesign work for all 36 pages, starting with dashboard.ejs (2683 lines, ~13 tables/widgets — the biggest single page in the admin panel).</t>
+  </si>
+  <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
   </si>
   <si>
     <t>Planned</t>
   </si>
   <si>
-    <t>Phases 1-4 shipped (Overview + Classrooms, Students, Teachers + Instructors, Terms) — see Known Issues &amp; Fixes. Client approved the design direction and asked for the full page rebuilt in the same professional style with every existing action preserved. Remaining: Attendance tab, including the weekly stats chart, same approach each time (redesign, verify every existing action live, ship).</t>
+    <t>Phases 1-4 shipped (Overview + Classrooms, Students, Teachers + Instructors, Terms) — see Known Issues &amp; Fixes. Remaining: Attendance tab, including the weekly stats chart.</t>
   </si>
   <si>
     <t>Blockly Lab</t>
@@ -274,10 +283,7 @@
     <t>Expand block set to match full Scratch/PictoBlox reference</t>
   </si>
   <si>
-    <t>Partially done</t>
-  </si>
-  <si>
-    <t>Client asked for every block in the reference doc to be implemented, including Video Sensing, Text-to-Speech and Translate. Phase 1 shipped: Motion + Looks gaps (16 blocks: rotation/position/graphic-effects/layers/reporters). Phase 2 shipped: Events + Sensing gaps (10 blocks: broadcast-and-wait that genuinely waits, when-backdrop-switches, when-timer&gt;-value, touching/distance-to a named sprite and the mouse, a generic attribute-of-sprite reporter, date/time, days-since-2000, username) — each verified live via direct runtime-function calls. Remaining, deliberately deferred as its own subsystems rather than half-built: touching-color/color-touching-color (needs a pixel-sampling stage compositor), loudness (needs Web Audio/microphone access), drag mode (conflicts with the editor's existing always-on sprite dragging — needs a design decision first), Pen gaps (stamp, pen color/property variants), Music extension and a new Sound category (both need new sound-asset infrastructure), a true per-sprite costume list, Text-to-Speech (Web Speech API), Translate (needs an API/key decision), Video Sensing (webcam access).</t>
+    <t>Client asked for every block in the reference doc to be implemented, including Video Sensing, Text-to-Speech and Translate. Phase 1 shipped: Motion + Looks gaps (16 blocks). Phase 2 shipped: Events + Sensing gaps (10 blocks: broadcast-and-wait, when-backdrop-switches, when-timer&gt;-value, touching/distance-to a named sprite and the mouse, a generic attribute-of-sprite reporter, date/time, days-since-2000, username). Remaining, deliberately deferred as its own subsystems: touching-color (pixel-sampling stage compositor), loudness (Web Audio/mic access), drag mode (conflicts with the editor's existing always-on sprite dragging), Pen gaps, Music extension + a new Sound category (both need sound-asset infrastructure), a true per-sprite costume list, Text-to-Speech, Translate, Video Sensing.</t>
   </si>
   <si>
     <t>Arcade</t>
@@ -1341,13 +1347,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1369,13 +1375,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1823,7 +1829,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1853,7 +1859,7 @@
       <c r="B2" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>82</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1862,41 +1868,41 @@
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>92</v>
@@ -1904,12 +1910,12 @@
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>82</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1918,16 +1924,30 @@
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1948,13 +1968,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1962,912 +1982,912 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2875,13 +2895,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2889,13 +2909,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2903,13 +2923,13 @@
         <v>64</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2917,13 +2937,13 @@
         <v>64</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2931,13 +2951,13 @@
         <v>64</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2945,13 +2965,13 @@
         <v>64</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2959,13 +2979,13 @@
         <v>64</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2973,97 +2993,97 @@
         <v>64</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="277">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-16</t>
+    <t>Generated 2026-10-17</t>
   </si>
   <si>
     <t>Category</t>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Every .jk-select dropdown stretched full-width and stacked instead of sitting inline in its toolbar</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the admin Dashboard page's Overview tab: the browser's global `select { width: 100% }` rule (style.css, meant for plain form inputs) was never overridden by .jk-select, so every filter dropdown using that class stretched to fill its flex container and stacked one per row instead of flowing inline next to the search box and buttons. This was already live on School Details' Students/Teachers classroom-filter dropdowns too — just not obvious there since each toolbar only had one dropdown, so nothing visibly competed for the row. Fixed once in the shared stylesheet (width:auto + margin-bottom:0) — benefits every current and future .jk-select on any admin page. Verified live on both the new Dashboard toolbar and the existing School Details Students tab toolbar (screenshotted both, confirmed single-row layout).</t>
+  </si>
+  <si>
     <t>School Details tables: per-row action button (generate avatar, mark active/inactive, archive, etc.) could become invisible</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Client reported the Students tab's row actions (generate login PIN info, avatar, active/inactive, archive) 'are no more there.' Confirmed the server was sending the correct HTML every time (checked with the client's own real school's real student data, not synthetic test data) and that nothing in the Phase 1-4 redesign had dropped the consolidated action button or its modal. Ruled out, in order, with evidence each time: browser cache (a hard refresh didn't fix it), extensions (reproduced the same way in Incognito), and horizontal overflow (pinned the actions column to the right edge of the table with position:sticky as a robustness improvement regardless — Students/Teachers/Instructors tables all share this now — but the client's own follow-up screenshot showed the button's hover-highlight box rendering in the right place, meaning the real bug was inside the button, not the column). The actual cause: the row-action icon's three &lt;circle&gt; dots had fill="none" stroke="currentColor" at r=1.3 — far too faint a hairline outline to see at that size (should have been solid filled dots) — and, more fundamentally, the &lt;svg&gt;'s computed width was collapsing to 0px in the browser despite an explicit width="16" attribute (confirmed live: no CSS rule in any loaded stylesheet matches the element, so the exact layout mechanism behind the collapse wasn't pinned down, only reproduced and fixed). Fixed by filling the dots solid and forcing the icon's size via inline CSS instead of relying on the attribute alone. Verified live by rasterizing the actual rendered element and confirming real non-transparent pixels, plus a visual close-up screenshot showing three clearly visible dots.</t>
   </si>
   <si>
@@ -265,7 +271,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Step 1 shipped: fixed the shared .sortable-table sort-arrow infrastructure (a pre-existing CSS typo — font-size: px with no value — meant clicking a sortable header never visibly showed anything; also added a guard so checkbox/icon-only-action columns don't get a pointless sort arrow) — this alone improved all 9 pages that already used .sortable-table before any visual redesign touches them. Still pending: the actual page-by-page redesign work for all 36 pages, starting with dashboard.ejs (2683 lines, ~13 tables/widgets — the biggest single page in the admin panel).</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page, Phase 1 (Overview tab) shipped: 8 stat cards, the user filter toolbar, the All Registered Users table (consolidated View/Edit/Archive into one row-action button + modal, matching School Details' pattern), verified live against real platform data (487 users). Dashboard has 6 more tabs (Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks) before moving to the next page; then 35 more pages across Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1333,13 +1339,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,13 +1381,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1392,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1445,21 +1451,21 @@
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>24</v>
@@ -1473,7 +1479,7 @@
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>26</v>
@@ -1487,7 +1493,7 @@
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>28</v>
@@ -1501,7 +1507,7 @@
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
@@ -1515,7 +1521,7 @@
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>32</v>
@@ -1529,7 +1535,7 @@
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>34</v>
@@ -1543,7 +1549,7 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>36</v>
@@ -1557,7 +1563,7 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>38</v>
@@ -1571,7 +1577,7 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>40</v>
@@ -1660,11 +1666,11 @@
       <c r="B19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1672,10 +1678,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>56</v>
@@ -1711,41 +1717,41 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>17</v>
+      <c r="C25" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>68</v>
@@ -1767,21 +1773,21 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>74</v>
@@ -1795,21 +1801,21 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>79</v>
@@ -1819,6 +1825,20 @@
       </c>
       <c r="D30" s="5" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1857,13 +1877,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1871,83 +1891,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1968,13 +1988,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -1982,1108 +2002,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="279">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-17</t>
+    <t>Generated 2026-10-18</t>
   </si>
   <si>
     <t>Category</t>
@@ -64,6 +64,15 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Dashboard page: all 7 tabs' data load unconditionally on every page visit (perf)</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Found while verifying the Learning tab redesign: clicking "View Analytics" on a course appeared to silently do nothing (no error anywhere) — root-caused via a monkey-patched wrapper around the click handler to the dashboard page firing loadDashboardOverview/loadBusinessDashboard/loadLearningDashboard/loadSchoolsDashboard/loadFinanceDashboard/loadEngagementDashboard unconditionally on every load regardless of which tab is active (loadDashboardOverview is even called twice), which can saturate the browser's per-origin connection pool and delay a just-clicked fetch several seconds past what a quick manual check would wait for. Confirmed the click always invokes the handler immediately and the promise does eventually resolve correctly (worked fine on a true confirm wait) — not a correctness bug, just a real performance/UX smell worth fixing by lazy-loading each tab's data on first open, matching the pattern already used for Attendance on the School Details page. Also noticed in passing: the Learning tab's Course Analytics modal can show a Completion Rate over 100% (seen: 1329%) for at least one course — a separate, pre-existing backend calculation issue, not touched.</t>
+  </si>
+  <si>
     <t>Every .jk-select dropdown stretched full-width and stacked instead of sitting inline in its toolbar</t>
   </si>
   <si>
@@ -181,9 +190,6 @@
     <t>Instructor/Admin share one access check (ensureInstructorOrAdmin)</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>Instructor-scoped pages rely entirely on query-level scoping, not the route guard, to keep instructors out of each other's data.</t>
   </si>
   <si>
@@ -271,7 +277,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page, Phase 1 (Overview tab) shipped: 8 stat cards, the user filter toolbar, the All Registered Users table (consolidated View/Edit/Archive into one row-action button + modal, matching School Details' pattern), verified live against real platform data (487 users). Dashboard has 6 more tabs (Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks) before moving to the next page; then 35 more pages across Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page shipped so far: Phase 1 Overview tab (8 stat cards, filter toolbar, consolidated row-action button + modal), Phase 2 Business KPIs tab (9 stat cards, 4 tables with pill-badge statuses), Phase 3 Learning tab (4 stat cards, Top Courses table, a wide Course Analytics modal with 8 stat cards + 2 sortable student tables). Verified live against real platform data throughout (487 users, 31 courses). Dashboard has 4 more tabs (Schools, Finance, Engagement, Reports &amp; Pitch Decks) before moving to the next page; then 35 more pages across Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -872,11 +878,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
@@ -901,12 +907,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1342,10 +1348,10 @@
         <v>27</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1384,10 +1390,10 @@
         <v>104</v>
       </c>
       <c r="C9" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1398,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1442,11 +1448,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1454,24 +1460,24 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>17</v>
+      <c r="C5" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1479,128 +1485,128 @@
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>17</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1608,13 +1614,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1622,13 +1628,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1636,13 +1642,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1650,13 +1656,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>17</v>
+        <v>51</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1664,13 +1670,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1678,10 +1684,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>56</v>
@@ -1708,8 +1714,8 @@
       <c r="B22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
+      <c r="C22" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>60</v>
@@ -1722,8 +1728,8 @@
       <c r="B23" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>17</v>
+      <c r="C23" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>62</v>
@@ -1731,35 +1737,35 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>69</v>
@@ -1778,8 +1784,8 @@
       <c r="B27" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>17</v>
+      <c r="C27" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>72</v>
@@ -1787,27 +1793,27 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
+      <c r="C29" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>77</v>
@@ -1815,30 +1821,44 @@
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>17</v>
+      <c r="C31" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1877,13 +1897,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1891,83 +1911,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>87</v>
+        <v>99</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>87</v>
+        <v>101</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1988,13 +2008,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2002,1108 +2022,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>107</v>
+        <v>117</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>107</v>
+        <v>119</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>107</v>
+        <v>121</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>107</v>
+        <v>125</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>107</v>
+        <v>127</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>107</v>
+        <v>129</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>107</v>
+        <v>131</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>107</v>
+        <v>133</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>107</v>
+        <v>135</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>107</v>
+        <v>137</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>107</v>
+        <v>140</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>107</v>
+        <v>144</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>107</v>
+        <v>146</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>107</v>
+        <v>148</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>107</v>
+        <v>150</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>107</v>
+        <v>152</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>107</v>
+        <v>154</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>107</v>
+        <v>157</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>107</v>
+        <v>159</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>107</v>
+        <v>161</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>107</v>
+        <v>163</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>107</v>
+        <v>165</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>107</v>
+        <v>167</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>107</v>
+        <v>169</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>107</v>
+        <v>171</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>107</v>
+        <v>174</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>107</v>
+        <v>176</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>107</v>
+        <v>178</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>107</v>
+        <v>180</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>107</v>
+        <v>182</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>107</v>
+        <v>184</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>107</v>
+        <v>186</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>107</v>
+        <v>188</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>107</v>
+        <v>190</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>107</v>
+        <v>193</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>107</v>
+        <v>195</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>107</v>
+        <v>197</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>107</v>
+        <v>202</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>107</v>
+        <v>204</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>107</v>
+        <v>206</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>107</v>
+        <v>209</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>107</v>
+        <v>211</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>107</v>
+        <v>213</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>107</v>
+        <v>215</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>107</v>
+        <v>220</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>107</v>
+        <v>225</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>107</v>
+        <v>227</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>107</v>
+        <v>229</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>107</v>
+        <v>231</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>107</v>
+        <v>234</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>107</v>
+        <v>242</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>107</v>
+        <v>244</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>107</v>
+        <v>246</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>107</v>
+        <v>248</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>107</v>
+        <v>250</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>107</v>
+        <v>252</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>107</v>
+        <v>254</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>107</v>
+        <v>259</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>107</v>
+        <v>261</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>107</v>
+        <v>263</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>107</v>
+        <v>265</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>107</v>
+        <v>268</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>107</v>
+        <v>270</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>107</v>
+        <v>272</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>107</v>
+        <v>274</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>107</v>
+        <v>276</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>107</v>
+        <v>278</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="283">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,6 +64,21 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Dashboard's Engagement tab Filter button called a function that didn't exist (applyActivityFilters)</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Engagement tab: clicking Filter threw "applyActivityFilters is not defined" and did nothing — the function was referenced in the button's onclick but never defined anywhere in the file. The backend route (/admin/dashboard/engagement) already correctly supports the action/startDate/endDate query params loadEngagementDashboard() reads, so this was purely a missing client-side wire-up. Fixed by adding the function, resetting to page 1 (not appending) so new filters replace the current list. Verified live: calling it no longer throws and the typeof check confirms it's now a real function.</t>
+  </si>
+  <si>
+    <t>input[type="date"] fields using .jk-select stretched full-width despite the Phase 1 select-width fix</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Engagement tab's date-range filter: the two date inputs stacked one per row instead of sitting inline, even though the same .jk-select class had already fixed this for plain &lt;select&gt; elements. Root cause: style.css's input[type="date"] rule has specificity (0,1,1) — a type selector plus an attribute selector — which beats a bare .jk-select class selector at (0,1,0) regardless of source order, whereas the earlier select{width:100%} rule was only (0,0,1) and lost cleanly. Fixed by rewriting the selector as `select.jk-select, input.jk-select` to tie the specificity at (0,1,1), letting the stylesheet's later position in &lt;head&gt; decide the cascade. Verified live: both date inputs now size to their content (144px) instead of 100%.</t>
+  </si>
+  <si>
     <t>Dashboard page: all 7 tabs' data load unconditionally on every page visit (perf)</t>
   </si>
   <si>
@@ -76,9 +91,6 @@
     <t>Every .jk-select dropdown stretched full-width and stacked instead of sitting inline in its toolbar</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the admin Dashboard page's Overview tab: the browser's global `select { width: 100% }` rule (style.css, meant for plain form inputs) was never overridden by .jk-select, so every filter dropdown using that class stretched to fill its flex container and stacked one per row instead of flowing inline next to the search box and buttons. This was already live on School Details' Students/Teachers classroom-filter dropdowns too — just not obvious there since each toolbar only had one dropdown, so nothing visibly competed for the row. Fixed once in the shared stylesheet (width:auto + margin-bottom:0) — benefits every current and future .jk-select on any admin page. Verified live on both the new Dashboard toolbar and the existing School Details Students tab toolbar (screenshotted both, confirmed single-row layout).</t>
   </si>
   <si>
@@ -277,7 +289,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page shipped so far: Phase 1 Overview tab (8 stat cards, filter toolbar, consolidated row-action button + modal), Phase 2 Business KPIs tab (9 stat cards, 4 tables with pill-badge statuses), Phase 3 Learning tab (4 stat cards, Top Courses table, a wide Course Analytics modal with 8 stat cards + 2 sortable student tables). Verified live against real platform data throughout (487 users, 31 courses). Dashboard has 4 more tabs (Schools, Finance, Engagement, Reports &amp; Pitch Decks) before moving to the next page; then 35 more pages across Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Next: moving to the Schools/Students page group (schools.ejs, students.ejs, archive.ejs, classroom-dashboard.ejs, studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs), per the agreed usage-frequency order, then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -878,11 +890,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
     </font>
     <font>
       <b/>
@@ -907,12 +919,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1345,13 +1357,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,13 +1399,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1404,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1448,11 +1460,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1460,10 +1472,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1476,8 +1488,8 @@
       <c r="B5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>20</v>
+      <c r="C5" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1485,41 +1497,41 @@
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>20</v>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>32</v>
@@ -1527,13 +1539,13 @@
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>20</v>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>34</v>
@@ -1541,13 +1553,13 @@
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>20</v>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>36</v>
@@ -1555,13 +1567,13 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>20</v>
+      <c r="C11" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>38</v>
@@ -1569,13 +1581,13 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>20</v>
+      <c r="C12" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>40</v>
@@ -1583,13 +1595,13 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>20</v>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>42</v>
@@ -1597,13 +1609,13 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>20</v>
+      <c r="C14" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
@@ -1611,13 +1623,13 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>20</v>
+      <c r="C15" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1625,13 +1637,13 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>20</v>
+      <c r="C16" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>48</v>
@@ -1644,8 +1656,8 @@
       <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>20</v>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>50</v>
@@ -1658,8 +1670,8 @@
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>20</v>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>52</v>
@@ -1672,8 +1684,8 @@
       <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>20</v>
+      <c r="C19" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>54</v>
@@ -1686,8 +1698,8 @@
       <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>20</v>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>56</v>
@@ -1714,8 +1726,8 @@
       <c r="B22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>20</v>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>60</v>
@@ -1729,7 +1741,7 @@
         <v>61</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>62</v>
@@ -1742,8 +1754,8 @@
       <c r="B24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>20</v>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>64</v>
@@ -1751,55 +1763,55 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>74</v>
@@ -1807,16 +1819,16 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1824,41 +1836,69 @@
         <v>15</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="5" t="s">
+    </row>
+    <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>84</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1897,13 +1937,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1911,83 +1951,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>89</v>
+        <v>103</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2008,13 +2048,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2022,1108 +2062,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>109</v>
+        <v>119</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>109</v>
+        <v>121</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>109</v>
+        <v>123</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>109</v>
+        <v>125</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>109</v>
+        <v>127</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>109</v>
+        <v>129</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>109</v>
+        <v>131</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>109</v>
+        <v>133</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>109</v>
+        <v>135</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>109</v>
+        <v>137</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>109</v>
+        <v>139</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>109</v>
+        <v>141</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>109</v>
+        <v>144</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>109</v>
+        <v>146</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>109</v>
+        <v>148</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>109</v>
+        <v>150</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>109</v>
+        <v>152</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>109</v>
+        <v>154</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>109</v>
+        <v>156</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>109</v>
+        <v>158</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>109</v>
+        <v>161</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>109</v>
+        <v>163</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>109</v>
+        <v>165</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>109</v>
+        <v>167</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>109</v>
+        <v>169</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>109</v>
+        <v>171</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>109</v>
+        <v>173</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>109</v>
+        <v>175</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>109</v>
+        <v>178</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>109</v>
+        <v>180</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>109</v>
+        <v>182</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>109</v>
+        <v>184</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>109</v>
+        <v>186</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>109</v>
+        <v>188</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>109</v>
+        <v>190</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>109</v>
+        <v>192</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>109</v>
+        <v>194</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>109</v>
+        <v>197</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>109</v>
+        <v>199</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>109</v>
+        <v>201</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>109</v>
+        <v>206</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>109</v>
+        <v>208</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>109</v>
+        <v>210</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>109</v>
+        <v>213</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>109</v>
+        <v>215</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>109</v>
+        <v>217</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>109</v>
+        <v>219</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>109</v>
+        <v>224</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>109</v>
+        <v>229</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>109</v>
+        <v>231</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>109</v>
+        <v>233</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>109</v>
+        <v>235</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>109</v>
+        <v>238</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>109</v>
+        <v>246</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>109</v>
+        <v>248</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>109</v>
+        <v>250</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>109</v>
+        <v>252</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>109</v>
+        <v>254</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>109</v>
+        <v>256</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>109</v>
+        <v>258</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>109</v>
+        <v>263</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>109</v>
+        <v>265</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>109</v>
+        <v>267</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>109</v>
+        <v>269</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>109</v>
+        <v>272</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>109</v>
+        <v>274</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>109</v>
+        <v>276</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>109</v>
+        <v>278</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>109</v>
+        <v>280</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>109</v>
+        <v>282</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="285">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Students page (/admin/students) was a standalone page with no shared nav, and 500'd when brought onto it</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: it was the only admin page NOT using the shared partials/adminHeader.ejs — a standalone HTML document with just a logo and a "Back to Dashboard" link, no top nav menu at all, plus its own full duplicate copy (~75 lines) of the sortable-table JS that already lives in adminHeader.ejs. Converting it onto the shared header immediately 500'd: adminHeader.ejs's nav reads a `role` local to decide what to render ("Dashboard ▾" vs a plain link etc.), and listStudents() never passed one since this page never needed it before. Fixed by adding role: "admin" to the controller's res.render() call. Also removed the now-redundant duplicate sort JS (the shared one already has the Phase-1 arrow fix). Verified live: full nav now present, both tables (students, parents) render and sort correctly, no more 500.</t>
+  </si>
+  <si>
     <t>Dashboard's Engagement tab Filter button called a function that didn't exist (applyActivityFilters)</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the Engagement tab: clicking Filter threw "applyActivityFilters is not defined" and did nothing — the function was referenced in the button's onclick but never defined anywhere in the file. The backend route (/admin/dashboard/engagement) already correctly supports the action/startDate/endDate query params loadEngagementDashboard() reads, so this was purely a missing client-side wire-up. Fixed by adding the function, resetting to page 1 (not appending) so new filters replace the current list. Verified live: calling it no longer throws and the typeof check confirms it's now a real function.</t>
   </si>
   <si>
@@ -289,7 +295,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Next: moving to the Schools/Students page group (schools.ejs, students.ejs, archive.ejs, classroom-dashboard.ejs, studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs), per the agreed usage-frequency order, then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. Remaining in this group: archive.ejs, classroom-dashboard.ejs, studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1357,13 +1363,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1399,13 +1405,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1416,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1474,11 +1480,11 @@
       <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1486,10 +1492,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1525,21 +1531,21 @@
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>33</v>
@@ -1553,7 +1559,7 @@
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>35</v>
@@ -1567,7 +1573,7 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>37</v>
@@ -1581,7 +1587,7 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>39</v>
@@ -1595,7 +1601,7 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
@@ -1609,7 +1615,7 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1623,7 +1629,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
@@ -1637,7 +1643,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -1651,7 +1657,7 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
@@ -1740,8 +1746,8 @@
       <c r="B23" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>22</v>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>62</v>
@@ -1754,8 +1760,8 @@
       <c r="B24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>17</v>
+      <c r="C24" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>64</v>
@@ -1791,41 +1797,41 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
+      <c r="C29" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>76</v>
@@ -1847,21 +1853,21 @@
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>82</v>
@@ -1875,21 +1881,21 @@
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>87</v>
@@ -1899,6 +1905,20 @@
       </c>
       <c r="D34" s="5" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1937,13 +1957,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1951,83 +1971,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2048,13 +2068,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2062,1108 +2082,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -295,7 +295,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. Remaining in this group: archive.ejs, classroom-dashboard.ejs, studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). Remaining in this group: classroom-dashboard.ejs, studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -295,7 +295,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). Remaining in this group: classroom-dashboard.ejs, studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). Remaining in this group: studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -295,7 +295,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). Remaining in this group: studentProgress.ejs, studentEnrollments.ejs, schoolCourses.ejs, parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). Remaining in this group: parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-18</t>
+    <t>Generated 2026-10-19</t>
   </si>
   <si>
     <t>Category</t>
@@ -295,7 +295,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). Remaining in this group: parentInvoices.ejs, quotes.ejs, editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). Remaining in this group: editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="287">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Edit User page: Role dropdown always pre-selected "Admin" regardless of the edited user's actual role (silent privilege-escalation risk)</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: the Role &lt;select&gt;'s "selected" logic compared each option against `role` — the local meant for adminHeader.ejs's own nav permission check, which the controller always hardcodes to "admin" for the logged-in admin's own session — instead of `user.role`, the role of the user actually being edited. The practical effect: opening Edit User for ANY student/teacher/parent/instructor showed "Admin" pre-selected in the Role dropdown, and submitting the form without deliberately changing it back would silently promote that user to admin. Fixed by comparing each option against `user.role` instead. Verified live: created a throwaway student account, opened its Edit User page, confirmed the dropdown now correctly pre-selects "Student", submitted the form without touching the dropdown, and confirmed via a direct DB read that the role stayed "student" (previously would have flipped to "admin").</t>
+  </si>
+  <si>
     <t>Students page (/admin/students) was a standalone page with no shared nav, and 500'd when brought onto it</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: it was the only admin page NOT using the shared partials/adminHeader.ejs — a standalone HTML document with just a logo and a "Back to Dashboard" link, no top nav menu at all, plus its own full duplicate copy (~75 lines) of the sortable-table JS that already lives in adminHeader.ejs. Converting it onto the shared header immediately 500'd: adminHeader.ejs's nav reads a `role` local to decide what to render ("Dashboard ▾" vs a plain link etc.), and listStudents() never passed one since this page never needed it before. Fixed by adding role: "admin" to the controller's res.render() call. Also removed the now-redundant duplicate sort JS (the shared one already has the Phase-1 arrow fix). Verified live: full nav now present, both tables (students, parents) render and sort correctly, no more 500.</t>
   </si>
   <si>
@@ -295,7 +301,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). Remaining in this group: editUser.ejs — then Courses/Pathways, Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (8 pages). Next: Courses/Pathways group (courses.ejs, singleCourse.ejs, pathways.ejs, pathwayCourses.ejs, guides.ejs), then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1363,13 +1369,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,13 +1411,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1494,11 +1500,11 @@
       <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1506,10 +1512,10 @@
         <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>27</v>
@@ -1545,21 +1551,21 @@
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>35</v>
@@ -1573,7 +1579,7 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>37</v>
@@ -1587,7 +1593,7 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>39</v>
@@ -1601,7 +1607,7 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
@@ -1615,7 +1621,7 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1629,7 +1635,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
@@ -1643,7 +1649,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -1657,7 +1663,7 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
@@ -1671,7 +1677,7 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
@@ -1760,8 +1766,8 @@
       <c r="B24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>24</v>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>64</v>
@@ -1774,8 +1780,8 @@
       <c r="B25" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>17</v>
+      <c r="C25" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>66</v>
@@ -1811,41 +1817,41 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>17</v>
+      <c r="C30" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>78</v>
@@ -1867,21 +1873,21 @@
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>84</v>
@@ -1895,21 +1901,21 @@
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>89</v>
@@ -1919,6 +1925,20 @@
       </c>
       <c r="D35" s="5" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1957,13 +1977,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1971,83 +1991,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2068,13 +2088,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2082,1108 +2102,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -301,7 +301,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (8 pages). Next: Courses/Pathways group (courses.ejs, singleCourse.ejs, pathways.ejs, pathwayCourses.ejs, guides.ejs), then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). Remaining in this group: singleCourse.ejs, pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="289">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-19</t>
+    <t>Generated 2026-10-20</t>
   </si>
   <si>
     <t>Category</t>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Single Course page: "+ Add Module" button threw an error and did nothing, on every course</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Modules tab: singleCourse.ejs declared its own global openModal()/closeModal() (no id parameter, hardcoded to a #createModal element that doesn't exist anywhere on this page or any of its 6 tab partials) in a &lt;script&gt; block positioned AFTER modules.ejs's own parameterized openModal(id)/closeModal(id) gets included. Both are plain function declarations in the same global scope, so the later one silently wins — meaning clicking "+ Add Module" threw "Cannot read properties of null (reading 'style')" and did nothing, in production, on every course's Modules tab, independent of anything in this redesign pass. Also found and removed openCreateModal()/closeCreateModal()/openDeleteModal()/closeDeleteModal() in the same file — all dead code with no matching element and no caller anywhere on this page or its partials, likely copy-pasted from courses.ejs (which does have a real #createModal). Kept the one duplicate that IS actually used (openEditModal/closeEditModal) in a single place, and kept the generic "close any .modal on outside click" handler. Verified live: Add Module modal now opens correctly with zero page errors, down from one fatal TypeError on every click.</t>
+  </si>
+  <si>
     <t>Edit User page: Role dropdown always pre-selected "Admin" regardless of the edited user's actual role (silent privilege-escalation risk)</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: the Role &lt;select&gt;'s "selected" logic compared each option against `role` — the local meant for adminHeader.ejs's own nav permission check, which the controller always hardcodes to "admin" for the logged-in admin's own session — instead of `user.role`, the role of the user actually being edited. The practical effect: opening Edit User for ANY student/teacher/parent/instructor showed "Admin" pre-selected in the Role dropdown, and submitting the form without deliberately changing it back would silently promote that user to admin. Fixed by comparing each option against `user.role` instead. Verified live: created a throwaway student account, opened its Edit User page, confirmed the dropdown now correctly pre-selects "Student", submitted the form without touching the dropdown, and confirmed via a direct DB read that the role stayed "student" (previously would have flipped to "admin").</t>
   </si>
   <si>
@@ -301,7 +307,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). Remaining in this group: singleCourse.ejs, pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Remaining: Lessons/Assignment/Capstone Project/External Projects tabs on singleCourse.ejs, then pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1369,13 +1375,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1411,13 +1417,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1428,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1514,11 +1520,11 @@
       <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1526,10 +1532,10 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -1565,21 +1571,21 @@
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>37</v>
@@ -1593,7 +1599,7 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>39</v>
@@ -1607,7 +1613,7 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
@@ -1621,7 +1627,7 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1635,7 +1641,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
@@ -1649,7 +1655,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -1663,7 +1669,7 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
@@ -1677,7 +1683,7 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
@@ -1691,7 +1697,7 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>53</v>
@@ -1780,8 +1786,8 @@
       <c r="B25" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>26</v>
+      <c r="C25" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>66</v>
@@ -1794,8 +1800,8 @@
       <c r="B26" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>17</v>
+      <c r="C26" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>68</v>
@@ -1831,41 +1837,41 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>17</v>
+      <c r="C31" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>80</v>
@@ -1887,21 +1893,21 @@
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>86</v>
@@ -1915,21 +1921,21 @@
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>91</v>
@@ -1939,6 +1945,20 @@
       </c>
       <c r="D36" s="5" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1977,13 +1997,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1991,83 +2011,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2088,13 +2108,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2102,1108 +2122,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -307,7 +307,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Remaining: Lessons/Assignment/Capstone Project/External Projects tabs on singleCourse.ejs, then pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Remaining: Assignment/Capstone Project/External Projects tabs on singleCourse.ejs, then pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="291">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Single Course page: editing an assignment's instructions could silently overwrite the Module line instead</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Assignment tab: the AJAX-appended "create" card template was missing the "Assignment ID: X" paragraph that the server-rendered card has, so the two card variants ended up with a different number of &lt;p&gt; elements (2 vs 3). The edit-success handler patched the DOM via the fragile `p:nth-of-type(2)` position selector — correct for an AJAX-created card (Module, Instructions) but wrong for any server-rendered card (ID, Module, Instructions), where it silently overwrote the "Module: ..." line with the new instructions text instead of updating the actual instructions preview. Fixed by giving the instructions-preview paragraph a stable .assignment-preview-text class in both card templates and targeting that directly. Verified live: submitted a real edit and confirmed the Module paragraph stayed untouched while only the instructions preview updated.</t>
+  </si>
+  <si>
     <t>Single Course page: "+ Add Module" button threw an error and did nothing, on every course</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the Modules tab: singleCourse.ejs declared its own global openModal()/closeModal() (no id parameter, hardcoded to a #createModal element that doesn't exist anywhere on this page or any of its 6 tab partials) in a &lt;script&gt; block positioned AFTER modules.ejs's own parameterized openModal(id)/closeModal(id) gets included. Both are plain function declarations in the same global scope, so the later one silently wins — meaning clicking "+ Add Module" threw "Cannot read properties of null (reading 'style')" and did nothing, in production, on every course's Modules tab, independent of anything in this redesign pass. Also found and removed openCreateModal()/closeCreateModal()/openDeleteModal()/closeDeleteModal() in the same file — all dead code with no matching element and no caller anywhere on this page or its partials, likely copy-pasted from courses.ejs (which does have a real #createModal). Kept the one duplicate that IS actually used (openEditModal/closeEditModal) in a single place, and kept the generic "close any .modal on outside click" handler. Verified live: Add Module modal now opens correctly with zero page errors, down from one fatal TypeError on every click.</t>
   </si>
   <si>
@@ -307,7 +313,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Remaining: Assignment/Capstone Project/External Projects tabs on singleCourse.ejs, then pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). Remaining in this group: pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1375,13 +1381,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1417,13 +1423,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1434,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1534,11 +1540,11 @@
       <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1546,10 +1552,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>31</v>
@@ -1585,21 +1591,21 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>39</v>
@@ -1613,7 +1619,7 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
@@ -1627,7 +1633,7 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1641,7 +1647,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
@@ -1655,7 +1661,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -1669,7 +1675,7 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
@@ -1683,7 +1689,7 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
@@ -1697,7 +1703,7 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>53</v>
@@ -1711,7 +1717,7 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>55</v>
@@ -1800,8 +1806,8 @@
       <c r="B26" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>28</v>
+      <c r="C26" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>68</v>
@@ -1814,8 +1820,8 @@
       <c r="B27" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>17</v>
+      <c r="C27" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>70</v>
@@ -1851,41 +1857,41 @@
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>17</v>
+      <c r="C32" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>82</v>
@@ -1907,21 +1913,21 @@
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>88</v>
@@ -1935,21 +1941,21 @@
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>93</v>
@@ -1959,6 +1965,20 @@
       </c>
       <c r="D37" s="5" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1997,13 +2017,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2011,83 +2031,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2108,13 +2128,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2122,1108 +2142,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="293">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Pathways page: Description field in every pathway's Edit modal was a plain textarea instead of CKEditor</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: the Description &lt;textarea&gt; had TWO id attributes (id="content" and id="edit-desc2-&lt;pathwayId&gt;") — invalid HTML, where the browser keeps only the first. Every pathway's edit modal actually had a textarea with id="content" (not unique — one per pathway card on the page), and the two CKEDITOR.replace() calls targeting "edit-desc-&lt;id&gt;" (missing a "2", itself wrong) and "edit-desc2-&lt;id&gt;" (referencing an id the browser had already dropped) both silently failed to find their target. The practical effect: the Description field in every pathway's edit modal was a plain, unstyled, non-rich-text textarea, while Target Audience and Expected Outcomes worked correctly right next to it. Fixed by removing the duplicate id attribute and the dead CKEDITOR.replace("edit-desc-...") call. Verified live: the edit modal now correctly initializes all three CKEditor instances (Description included) with zero duplicate id="content" elements on the page (previously one per pathway card).</t>
+  </si>
+  <si>
     <t>Single Course page: editing an assignment's instructions could silently overwrite the Module line instead</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the Assignment tab: the AJAX-appended "create" card template was missing the "Assignment ID: X" paragraph that the server-rendered card has, so the two card variants ended up with a different number of &lt;p&gt; elements (2 vs 3). The edit-success handler patched the DOM via the fragile `p:nth-of-type(2)` position selector — correct for an AJAX-created card (Module, Instructions) but wrong for any server-rendered card (ID, Module, Instructions), where it silently overwrote the "Module: ..." line with the new instructions text instead of updating the actual instructions preview. Fixed by giving the instructions-preview paragraph a stable .assignment-preview-text class in both card templates and targeting that directly. Verified live: submitted a real edit and confirmed the Module paragraph stayed untouched while only the instructions preview updated.</t>
   </si>
   <si>
@@ -313,7 +319,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). Remaining in this group: pathways.ejs, pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). Remaining in this group: pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1381,13 +1387,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,13 +1429,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1440,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1554,11 +1560,11 @@
       <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1566,10 +1572,10 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>33</v>
@@ -1605,21 +1611,21 @@
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
@@ -1633,7 +1639,7 @@
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1647,7 +1653,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
@@ -1661,7 +1667,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -1675,7 +1681,7 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
@@ -1689,7 +1695,7 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
@@ -1703,7 +1709,7 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>53</v>
@@ -1717,7 +1723,7 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>55</v>
@@ -1731,7 +1737,7 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>57</v>
@@ -1820,8 +1826,8 @@
       <c r="B27" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>30</v>
+      <c r="C27" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>70</v>
@@ -1834,8 +1840,8 @@
       <c r="B28" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>17</v>
+      <c r="C28" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>72</v>
@@ -1871,41 +1877,41 @@
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>17</v>
+      <c r="C33" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>84</v>
@@ -1927,21 +1933,21 @@
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>90</v>
@@ -1955,21 +1961,21 @@
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>95</v>
@@ -1979,6 +1985,20 @@
       </c>
       <c r="D38" s="5" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2017,13 +2037,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2031,83 +2051,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2128,13 +2148,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2142,1108 +2162,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="295">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Pathway Courses page threw a JS error on every load (missing #imageInput null check)</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Same bug class as singleCourse.ejs (see that entry below): a document.getElementById("imageInput").addEventListener(...) call with no null check, on a page with no #imageInput element at all, threw "Cannot read properties of null" on every single page load. Added a guard. Verified live: zero page errors after the fix, down from one fatal TypeError per load.</t>
+  </si>
+  <si>
     <t>Pathways page: Description field in every pathway's Edit modal was a plain textarea instead of CKEditor</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: the Description &lt;textarea&gt; had TWO id attributes (id="content" and id="edit-desc2-&lt;pathwayId&gt;") — invalid HTML, where the browser keeps only the first. Every pathway's edit modal actually had a textarea with id="content" (not unique — one per pathway card on the page), and the two CKEDITOR.replace() calls targeting "edit-desc-&lt;id&gt;" (missing a "2", itself wrong) and "edit-desc2-&lt;id&gt;" (referencing an id the browser had already dropped) both silently failed to find their target. The practical effect: the Description field in every pathway's edit modal was a plain, unstyled, non-rich-text textarea, while Target Audience and Expected Outcomes worked correctly right next to it. Fixed by removing the duplicate id attribute and the dead CKEDITOR.replace("edit-desc-...") call. Verified live: the edit modal now correctly initializes all three CKEditor instances (Description included) with zero duplicate id="content" elements on the page (previously one per pathway card).</t>
   </si>
   <si>
@@ -319,7 +325,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). Remaining in this group: pathwayCourses.ejs, guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). Remaining in this group: guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1387,13 +1393,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1429,13 +1435,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="4">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1574,11 +1580,11 @@
       <c r="B9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1586,10 +1592,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>35</v>
@@ -1625,21 +1631,21 @@
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1653,7 +1659,7 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
@@ -1667,7 +1673,7 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -1681,7 +1687,7 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>49</v>
@@ -1695,7 +1701,7 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
@@ -1709,7 +1715,7 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>53</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>55</v>
@@ -1737,7 +1743,7 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>57</v>
@@ -1751,7 +1757,7 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>59</v>
@@ -1840,8 +1846,8 @@
       <c r="B28" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>32</v>
+      <c r="C28" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>72</v>
@@ -1854,8 +1860,8 @@
       <c r="B29" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
+      <c r="C29" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>74</v>
@@ -1891,41 +1897,41 @@
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>17</v>
+      <c r="C34" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>86</v>
@@ -1947,21 +1953,21 @@
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>92</v>
@@ -1975,21 +1981,21 @@
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>97</v>
@@ -1999,6 +2005,20 @@
       </c>
       <c r="D39" s="5" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2037,13 +2057,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2051,83 +2071,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2148,13 +2168,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2162,1108 +2182,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -325,7 +325,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). Remaining in this group: guides.ejs — then Content/CMS, Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Next: Content/CMS group, then Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="300">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,10 +64,25 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Regenerate Thumbnail/Badge buttons gave zero feedback and looked frozen/broken while working</t>
+  </si>
+  <si>
+    <t>Fixed (UX only)</t>
+  </si>
+  <si>
+    <t>Client-reported: "course regenerate thumbnails is not working." Root-caused via live timing tests: utils/generateThumbnail.js launches a brand-new headless Chrome process and waits on an external Font Awesome CDN fetch (networkidle0) on every single regenerate call — measured 60-145 seconds for one request in this environment. The operation always eventually succeeded (confirmed via direct DB reads showing a fresh Cloudinary URL each time), but with zero loading state on the button, a wait that long is indistinguishable from a broken/frozen button — explains the "not working" report convincingly. Per explicit client direction, scoped this fix to the UX layer only: added handleConfirmSubmitWithLoading/setButtonLoading helpers (public/js/uiAlerts.js) and wired them into all 3 Regenerate Thumbnail/Badge buttons (courses.ejs, pathwayCourses.ejs, singleCourse.ejs's Modules tab) — the button now disables and relabels to "Generating... (can take up to a minute)" the instant the form submits. The underlying slowness (fresh browser launch + CDN wait per call, in a utility also shared by module badges and certificates) remains unfixed and out of scope for this pass — flagged as a separate, larger follow-up if wanted. Verified live: button's disabled+relabeled state confirmed at the exact moment form.submit() fires.</t>
+  </si>
+  <si>
+    <t>Guides page: Edit Guide modal had no close button, and no modal on this page closed on outside click</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Client-reported. Added a close (×) button to the modal (matching the .close span pattern used elsewhere) and a window.onclick outside-click handler (this page had none at all, unlike most other admin pages). Also added a platform-wide outside-click-to-close handler in partials/adminHeader.ejs for the shared .jk-modal-overlay class while investigating — covers every page already using that pattern (schools.ejs, students.ejs, quotes.ejs, parentInvoices.ejs) plus any future one, none of which had outside-click support before. Verified live: Guides modal closes via both the new × button and an outside click; schools.ejs's Edit School modal (previously no outside-click support) now closes correctly via the new global handler too.</t>
+  </si>
+  <si>
     <t>Pathway Courses page threw a JS error on every load (missing #imageInput null check)</t>
-  </si>
-  <si>
-    <t>Fixed</t>
   </si>
   <si>
     <t>Same bug class as singleCourse.ejs (see that entry below): a document.getElementById("imageInput").addEventListener(...) call with no null check, on a page with no #imageInput element at all, threw "Cannot read properties of null" on every single page load. Added a guard. Verified live: zero page errors after the fix, down from one fatal TypeError per load.</t>
@@ -1393,13 +1408,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,13 +1450,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="4">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1482,7 +1497,7 @@
       <c r="B2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1497,10 +1512,10 @@
         <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1508,13 +1523,13 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1522,13 +1537,13 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1536,13 +1551,13 @@
         <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1550,13 +1565,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1564,13 +1579,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1578,13 +1593,13 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1592,10 +1607,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="7" t="s">
         <v>34</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>35</v>
@@ -1609,7 +1624,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>37</v>
@@ -1622,11 +1637,11 @@
       <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>17</v>
+      <c r="C12" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1634,24 +1649,24 @@
         <v>15</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
@@ -1659,13 +1674,13 @@
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1673,128 +1688,128 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1802,13 +1817,13 @@
         <v>15</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1816,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1830,13 +1845,13 @@
         <v>15</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1844,13 +1859,13 @@
         <v>15</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1858,13 +1873,13 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>34</v>
+        <v>74</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1872,13 +1887,13 @@
         <v>15</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1886,13 +1901,13 @@
         <v>15</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>17</v>
+        <v>78</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1900,24 +1915,24 @@
         <v>15</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="8" t="s">
         <v>82</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>83</v>
@@ -1925,27 +1940,27 @@
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>88</v>
@@ -1953,27 +1968,27 @@
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>17</v>
+        <v>90</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>93</v>
@@ -1987,7 +2002,7 @@
         <v>94</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>95</v>
@@ -2001,7 +2016,7 @@
         <v>97</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>98</v>
@@ -2009,16 +2024,44 @@
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2057,13 +2100,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2071,83 +2114,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>102</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2168,13 +2211,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2182,1108 +2225,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="302">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,6 +64,15 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Edit FAQ page had invalid doubly-nested HTML (two &lt;html&gt;/&lt;head&gt;/&lt;body&gt; tags)</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Content/CMS group: editFaq.ejs had its own full &lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;...&lt;body&gt; wrapper AND included partials/adminHeader.ejs (which itself has a complete document shell) inside that body. Browsers silently collapse this, so it likely never visibly broke anything, but it's invalid markup that could behave unpredictably depending on browser quirks handling. Rewrote the page to just include the shared header like every other admin page. Also found and removed a dead CKEDITOR.replace('content') call on manageFaqs.ejs targeting an element that doesn't exist anywhere on that page (copy-paste leftover from editFaq.ejs, which does have #content). Verified live: editFaq's DOM now has exactly one &lt;html&gt;/&lt;head&gt;/&lt;body&gt; each.</t>
+  </si>
+  <si>
     <t>Regenerate Thumbnail/Badge buttons gave zero feedback and looked frozen/broken while working</t>
   </si>
   <si>
@@ -76,9 +85,6 @@
     <t>Guides page: Edit Guide modal had no close button, and no modal on this page closed on outside click</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Client-reported. Added a close (×) button to the modal (matching the .close span pattern used elsewhere) and a window.onclick outside-click handler (this page had none at all, unlike most other admin pages). Also added a platform-wide outside-click-to-close handler in partials/adminHeader.ejs for the shared .jk-modal-overlay class while investigating — covers every page already using that pattern (schools.ejs, students.ejs, quotes.ejs, parentInvoices.ejs) plus any future one, none of which had outside-click support before. Verified live: Guides modal closes via both the new × button and an outside click; schools.ejs's Edit School modal (previously no outside-click support) now closes correctly via the new global handler too.</t>
   </si>
   <si>
@@ -340,7 +346,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Next: Content/CMS group, then Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. Remaining in this group: company.ejs, benefits.ejs, editAbout.ejs, gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1408,13 +1414,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,13 +1456,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="4">
         <v>14</v>
       </c>
       <c r="D9" s="4">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1467,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1497,7 +1503,7 @@
       <c r="B2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1511,7 +1517,7 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1526,7 +1532,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1540,7 +1546,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1554,7 +1560,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>27</v>
@@ -1568,7 +1574,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -1582,7 +1588,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>31</v>
@@ -1596,7 +1602,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>33</v>
@@ -1610,7 +1616,7 @@
         <v>34</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>35</v>
@@ -1624,7 +1630,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>37</v>
@@ -1637,11 +1643,11 @@
       <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1649,10 +1655,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>42</v>
@@ -1666,7 +1672,7 @@
         <v>43</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
@@ -1680,7 +1686,7 @@
         <v>45</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1688,27 +1694,27 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>51</v>
@@ -1716,13 +1722,13 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>53</v>
@@ -1730,13 +1736,13 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>55</v>
@@ -1744,13 +1750,13 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>57</v>
@@ -1758,13 +1764,13 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>59</v>
@@ -1772,13 +1778,13 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>61</v>
@@ -1786,13 +1792,13 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>63</v>
@@ -1800,13 +1806,13 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>65</v>
@@ -1814,13 +1820,13 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>67</v>
@@ -1834,7 +1840,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>69</v>
@@ -1848,7 +1854,7 @@
         <v>70</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>71</v>
@@ -1862,7 +1868,7 @@
         <v>72</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>73</v>
@@ -1876,7 +1882,7 @@
         <v>74</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>75</v>
@@ -1890,7 +1896,7 @@
         <v>76</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>77</v>
@@ -1903,8 +1909,8 @@
       <c r="B31" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>39</v>
+      <c r="C31" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>79</v>
@@ -1917,8 +1923,8 @@
       <c r="B32" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>20</v>
+      <c r="C32" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>81</v>
@@ -1932,7 +1938,7 @@
         <v>82</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>83</v>
@@ -1946,7 +1952,7 @@
         <v>84</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>85</v>
@@ -1954,41 +1960,41 @@
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>20</v>
+      <c r="C37" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>93</v>
@@ -2002,7 +2008,7 @@
         <v>94</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>95</v>
@@ -2010,27 +2016,27 @@
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>100</v>
@@ -2038,30 +2044,44 @@
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>104</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2100,13 +2120,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2114,83 +2134,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2211,13 +2231,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2225,1108 +2245,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="304">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>CRITICAL: Company Info page (/admin/company) has been completely unloadable — a 500 error on every single visit</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Content/CMS group: companyController.js's showForm referenced `infoResult` in its res.render() locals object — a variable never declared anywhere in that function (likely a copy-paste leftover from a different controller's pattern that does define one). The ReferenceError on evaluating `infoResult` throws before res.render() is ever reached, independent of anything in this redesign pass — meaning this page has been fully broken (500 on every load) with no way to even view current settings, let alone edit them. Fixed by removing the bogus duplicate `info` key. Also fixed two real frontend bugs on the same page: the Hero Image file input had `required` on an edit form, forcing a fresh re-upload (or blocking submission) on every save even for unrelated text edits — confirmed the backend already falls back to the existing image when none is uploaded, so this was a pure frontend mistake; and three different fields (History, Company Name, Marquee Message) all shared id="content" (invalid duplicate-id HTML), meaning only History ever actually got CKEditor. Verified live: page now returns 200 with real company data (confirmed via direct request) instead of a 500, Hero Image input no longer required, zero duplicate ids.</t>
+  </si>
+  <si>
     <t>Edit FAQ page had invalid doubly-nested HTML (two &lt;html&gt;/&lt;head&gt;/&lt;body&gt; tags)</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the Content/CMS group: editFaq.ejs had its own full &lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;...&lt;body&gt; wrapper AND included partials/adminHeader.ejs (which itself has a complete document shell) inside that body. Browsers silently collapse this, so it likely never visibly broke anything, but it's invalid markup that could behave unpredictably depending on browser quirks handling. Rewrote the page to just include the shared header like every other admin page. Also found and removed a dead CKEDITOR.replace('content') call on manageFaqs.ejs targeting an element that doesn't exist anywhere on that page (copy-paste leftover from editFaq.ejs, which does have #content). Verified live: editFaq's DOM now has exactly one &lt;html&gt;/&lt;head&gt;/&lt;body&gt; each.</t>
   </si>
   <si>
@@ -346,7 +352,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. Remaining in this group: company.ejs, benefits.ejs, editAbout.ejs, gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". Remaining in this group: benefits.ejs, editAbout.ejs, gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1414,13 +1420,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,13 +1462,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="4">
         <v>14</v>
       </c>
       <c r="D9" s="4">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1473,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1517,11 +1523,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1529,10 +1535,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1657,11 +1663,11 @@
       <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1669,10 +1675,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
@@ -1708,21 +1714,21 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>52</v>
@@ -1736,7 +1742,7 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>54</v>
@@ -1750,7 +1756,7 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>56</v>
@@ -1764,7 +1770,7 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>58</v>
@@ -1778,7 +1784,7 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>60</v>
@@ -1792,7 +1798,7 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>62</v>
@@ -1806,7 +1812,7 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
@@ -1820,7 +1826,7 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
@@ -1834,7 +1840,7 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
@@ -1923,8 +1929,8 @@
       <c r="B32" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>41</v>
+      <c r="C32" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>81</v>
@@ -1937,8 +1943,8 @@
       <c r="B33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>17</v>
+      <c r="C33" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>83</v>
@@ -1974,41 +1980,41 @@
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>17</v>
+      <c r="C38" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>95</v>
@@ -2030,21 +2036,21 @@
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>101</v>
@@ -2058,21 +2064,21 @@
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>106</v>
@@ -2082,6 +2088,20 @@
       </c>
       <c r="D43" s="5" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2120,13 +2140,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2134,83 +2154,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2231,13 +2251,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2245,1108 +2265,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -352,7 +352,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". Remaining in this group: benefits.ejs, editAbout.ejs, gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). Remaining in this group: editAbout.ejs, gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="306">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>CRITICAL: Edit About Section has been completely non-functional — clicking Edit did nothing</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning the Content/CMS group: openEditModal() ends with document.getElementById("editModal").style.display = "block", but there was no element with id="editModal" anywhere on the live page — the &lt;form id="editForm"&gt; had lost its wrapping &lt;div id="editModal" class="modal"&gt; at some point (dead commented-out code directly above it in the same file still shows the wrapper, confirming it used to exist). Since getElementById("editModal") returned null, every click on "Edit" for any About section threw "Cannot set properties of null (reading 'style')" and did nothing — independent of anything in this redesign pass. Fixed by restoring the wrapping div. Also fixed a second bug on the same action: the Edit button passed only 5 of the 6 arguments openEditModal() expects, so imageUrl was always undefined and the modal's current-image preview never worked even once the modal itself could open — added the missing argument using the correct column name (section_image, confirmed against the schema; not image_url, which doesn't exist on this table). Verified live: Edit modal now opens correctly with the right section loaded and CKEditor initialized.</t>
+  </si>
+  <si>
     <t>CRITICAL: Company Info page (/admin/company) has been completely unloadable — a 500 error on every single visit</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the Content/CMS group: companyController.js's showForm referenced `infoResult` in its res.render() locals object — a variable never declared anywhere in that function (likely a copy-paste leftover from a different controller's pattern that does define one). The ReferenceError on evaluating `infoResult` throws before res.render() is ever reached, independent of anything in this redesign pass — meaning this page has been fully broken (500 on every load) with no way to even view current settings, let alone edit them. Fixed by removing the bogus duplicate `info` key. Also fixed two real frontend bugs on the same page: the Hero Image file input had `required` on an edit form, forcing a fresh re-upload (or blocking submission) on every save even for unrelated text edits — confirmed the backend already falls back to the existing image when none is uploaded, so this was a pure frontend mistake; and three different fields (History, Company Name, Marquee Message) all shared id="content" (invalid duplicate-id HTML), meaning only History ever actually got CKEditor. Verified live: page now returns 200 with real company data (confirmed via direct request) instead of a 500, Hero Image input no longer required, zero duplicate ids.</t>
   </si>
   <si>
@@ -352,7 +358,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). Remaining in this group: editAbout.ejs, gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). Remaining in this group: gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1420,13 +1426,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1462,13 +1468,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="4">
         <v>14</v>
       </c>
       <c r="D9" s="4">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1479,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1537,11 +1543,11 @@
       <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1549,10 +1555,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1677,11 +1683,11 @@
       <c r="B14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1689,10 +1695,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1728,21 +1734,21 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>54</v>
@@ -1756,7 +1762,7 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>56</v>
@@ -1770,7 +1776,7 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>58</v>
@@ -1784,7 +1790,7 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>60</v>
@@ -1798,7 +1804,7 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>62</v>
@@ -1812,7 +1818,7 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
@@ -1826,7 +1832,7 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
@@ -1840,7 +1846,7 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
@@ -1854,7 +1860,7 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>70</v>
@@ -1943,8 +1949,8 @@
       <c r="B33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>43</v>
+      <c r="C33" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>83</v>
@@ -1957,8 +1963,8 @@
       <c r="B34" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>17</v>
+      <c r="C34" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>85</v>
@@ -1994,41 +2000,41 @@
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>17</v>
+      <c r="C39" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>97</v>
@@ -2050,21 +2056,21 @@
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>103</v>
@@ -2078,21 +2084,21 @@
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>108</v>
@@ -2102,6 +2108,20 @@
       </c>
       <c r="D44" s="5" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2140,13 +2160,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2154,83 +2174,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2251,13 +2271,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2265,1108 +2285,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="308">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,6 +64,15 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Gallery page: "Edit" link on every image is dead (404) — the feature was never implemented</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: each image card linked to /admin/gallery/edit/:id, but no such route is registered (routes/galleryRoutes.js only has upload/create-category/delete-image/delete-category) and galleryController.js exports no editImage function at all. This looks like a genuinely unimplemented feature (not a regression — there's nothing to regress from) rather than a bug, so building a real edit flow (change title/category/replace the image) is out of scope for a styling/bug-fixing pass. Removed the dead link for now rather than ship something that 404s. Flagged here in case the client wants the feature built properly later.</t>
+  </si>
+  <si>
     <t>CRITICAL: Edit About Section has been completely non-functional — clicking Edit did nothing</t>
   </si>
   <si>
@@ -151,9 +160,6 @@
     <t>Dashboard page: all 7 tabs' data load unconditionally on every page visit (perf)</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>Found while verifying the Learning tab redesign: clicking "View Analytics" on a course appeared to silently do nothing (no error anywhere) — root-caused via a monkey-patched wrapper around the click handler to the dashboard page firing loadDashboardOverview/loadBusinessDashboard/loadLearningDashboard/loadSchoolsDashboard/loadFinanceDashboard/loadEngagementDashboard unconditionally on every load regardless of which tab is active (loadDashboardOverview is even called twice), which can saturate the browser's per-origin connection pool and delay a just-clicked fetch several seconds past what a quick manual check would wait for. Confirmed the click always invokes the handler immediately and the promise does eventually resolve correctly (worked fine on a true confirm wait) — not a correctness bug, just a real performance/UX smell worth fixing by lazy-loading each tab's data on first open, matching the pattern already used for Attendance on the School Details page. Also noticed in passing: the Learning tab's Course Analytics modal can show a Completion Rate over 100% (seen: 1329%) for at least one course — a separate, pre-existing backend calculation issue, not touched.</t>
   </si>
   <si>
@@ -358,7 +364,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). Remaining in this group: gallery.ejs, projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. Remaining in this group: projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -959,11 +965,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
@@ -988,12 +994,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1429,10 +1435,10 @@
         <v>39</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,10 +1477,10 @@
         <v>116</v>
       </c>
       <c r="C9" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1529,11 +1535,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1541,13 +1547,13 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1555,10 +1561,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1571,11 +1577,11 @@
       <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
+      <c r="C6" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1583,13 +1589,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1597,13 +1603,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1611,13 +1617,13 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1625,13 +1631,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1639,13 +1645,13 @@
         <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1653,13 +1659,13 @@
         <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>17</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1667,13 +1673,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1681,13 +1687,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1695,10 +1701,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1725,8 +1731,8 @@
       <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
+      <c r="C17" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>50</v>
@@ -1739,8 +1745,8 @@
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>17</v>
+      <c r="C18" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>52</v>
@@ -1748,27 +1754,27 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>17</v>
+      <c r="C20" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>57</v>
@@ -1776,13 +1782,13 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>17</v>
+      <c r="C21" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>59</v>
@@ -1790,13 +1796,13 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
+      <c r="C22" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>61</v>
@@ -1804,13 +1810,13 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>17</v>
+      <c r="C23" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>63</v>
@@ -1818,13 +1824,13 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>17</v>
+      <c r="C24" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>65</v>
@@ -1832,13 +1838,13 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>17</v>
+      <c r="C25" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>67</v>
@@ -1846,13 +1852,13 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>17</v>
+      <c r="C26" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>69</v>
@@ -1860,13 +1866,13 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>17</v>
+      <c r="C27" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>71</v>
@@ -1874,13 +1880,13 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>17</v>
+      <c r="C28" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>73</v>
@@ -1893,8 +1899,8 @@
       <c r="B29" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
+      <c r="C29" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>75</v>
@@ -1907,8 +1913,8 @@
       <c r="B30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>17</v>
+      <c r="C30" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>77</v>
@@ -1921,8 +1927,8 @@
       <c r="B31" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>17</v>
+      <c r="C31" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>79</v>
@@ -1935,8 +1941,8 @@
       <c r="B32" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>17</v>
+      <c r="C32" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>81</v>
@@ -1949,8 +1955,8 @@
       <c r="B33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>17</v>
+      <c r="C33" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>83</v>
@@ -1964,7 +1970,7 @@
         <v>84</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>85</v>
@@ -1991,8 +1997,8 @@
       <c r="B36" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>17</v>
+      <c r="C36" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>89</v>
@@ -2005,8 +2011,8 @@
       <c r="B37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>17</v>
+      <c r="C37" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>91</v>
@@ -2014,35 +2020,35 @@
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>98</v>
@@ -2061,8 +2067,8 @@
       <c r="B41" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>17</v>
+      <c r="C41" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>101</v>
@@ -2070,27 +2076,27 @@
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>17</v>
+      <c r="C43" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>106</v>
@@ -2098,30 +2104,44 @@
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>17</v>
+      <c r="C45" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2160,13 +2180,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2174,83 +2194,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>116</v>
+        <v>128</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>116</v>
+        <v>130</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2271,13 +2291,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2285,1108 +2305,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>136</v>
+        <v>142</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>136</v>
+        <v>150</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>136</v>
+        <v>152</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>136</v>
+        <v>156</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>136</v>
+        <v>158</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>136</v>
+        <v>160</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>136</v>
+        <v>162</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>136</v>
+        <v>164</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>136</v>
+        <v>166</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>136</v>
+        <v>169</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>136</v>
+        <v>171</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>136</v>
+        <v>173</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>136</v>
+        <v>175</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>136</v>
+        <v>177</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>136</v>
+        <v>179</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>136</v>
+        <v>181</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>136</v>
+        <v>183</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>136</v>
+        <v>186</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>136</v>
+        <v>188</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>136</v>
+        <v>190</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>136</v>
+        <v>192</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>136</v>
+        <v>194</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>136</v>
+        <v>196</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>136</v>
+        <v>198</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>136</v>
+        <v>200</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>136</v>
+        <v>203</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>136</v>
+        <v>205</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>136</v>
+        <v>207</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>136</v>
+        <v>209</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>136</v>
+        <v>211</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>136</v>
+        <v>213</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>136</v>
+        <v>215</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>136</v>
+        <v>217</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>136</v>
+        <v>219</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>136</v>
+        <v>222</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>136</v>
+        <v>224</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>136</v>
+        <v>226</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>136</v>
+        <v>231</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>136</v>
+        <v>233</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>136</v>
+        <v>235</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>136</v>
+        <v>238</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>136</v>
+        <v>240</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>136</v>
+        <v>242</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>136</v>
+        <v>244</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>136</v>
+        <v>249</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>136</v>
+        <v>254</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>136</v>
+        <v>256</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>136</v>
+        <v>258</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>136</v>
+        <v>260</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>136</v>
+        <v>263</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>136</v>
+        <v>271</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>136</v>
+        <v>273</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>136</v>
+        <v>275</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>136</v>
+        <v>277</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>136</v>
+        <v>279</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>136</v>
+        <v>281</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>136</v>
+        <v>283</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>136</v>
+        <v>288</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>136</v>
+        <v>290</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>136</v>
+        <v>292</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>136</v>
+        <v>294</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>136</v>
+        <v>297</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>136</v>
+        <v>299</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>136</v>
+        <v>301</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>136</v>
+        <v>303</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>136</v>
+        <v>305</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>136</v>
+        <v>307</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -364,7 +364,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. Remaining in this group: projectGalleryModeration.ejs — then Commerce, Communication, Other.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Next: Commerce group (pricingPlans.ejs), then Communication (events.ejs, eventRegistrations.ejs, newsletters.ejs, announcements.ejs), then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -364,7 +364,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Next: Commerce group (pricingPlans.ejs), then Communication (events.ejs, eventRegistrations.ejs, newsletters.ejs, announcements.ejs), then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Next: Communication group (events.ejs, eventRegistrations.ejs, newsletters.ejs, announcements.ejs), then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>Generated 2026-10-20</t>
+    <t>Generated 2026-10-21</t>
   </si>
   <si>
     <t>Category</t>
@@ -364,7 +364,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Next: Communication group (events.ejs, eventRegistrations.ejs, newsletters.ejs, announcements.ejs), then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). Remaining: newsletters.ejs, announcements.ejs — then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -364,7 +364,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). Remaining: newsletters.ejs, announcements.ejs — then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). Remaining: announcements.ejs — then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="310">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,6 +64,15 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>CRITICAL: Announcements page's search box and status filter crashed the whole table, showing zero rows</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: public/js/admin-announcements.js had the entire search/filter/table-click-delegation logic duplicated near the end of the file. The duplicate searchInput 'keyup' and statusFilter 'change' listeners both called renderAnnouncements() with no argument, but renderAnnouncements(data) immediately does tableBody.innerHTML = "" then reads data.length — since the correct AND broken listeners both fired on every keystroke/change, typing in the search box or changing the status filter reliably cleared the table then threw "Cannot read properties of undefined (reading 'length')", leaving the table empty with no way to recover short of a page reload. Confirmed live via Puppeteer: pageErrors showed the exact TypeError and a search for a common letter returned 0 rows instead of the matching announcements. Also removed in the same cleanup: a dead no-op delegated click handler checking for .editBtn/.publishBtn/.archiveBtn/.deleteBtn classes and a data-id attribute the actual rendered buttons never have (they use .btn-view/.btn-edit/.btn-success/.btn-warning/.btn-danger with onclick attributes directly), and a redundant duplicate loadAnnouncements() call at the bottom of the file causing a double fetch on every page load. Also found every class used by this page's JS-rendered table rows and modals (.btn-success/.btn-warning/.btn-danger/.action-buttons/.priority/.status/.text-muted/.text-center/.large-modal/.modal-header/.modal-footer/.form-group/.checkbox-group) had zero matching CSS anywhere in the codebase — confirmed via a grep across every stylesheet — so this page's modals and action buttons were rendering essentially unstyled even before today. Added a page-scoped &lt;style&gt; block using jk-* tokens. Verified live after the fix: zero page errors, search returns correct row counts, status filter works, View modal opens with real data.</t>
+  </si>
+  <si>
     <t>Gallery page: "Edit" link on every image is dead (404) — the feature was never implemented</t>
   </si>
   <si>
@@ -76,9 +85,6 @@
     <t>CRITICAL: Edit About Section has been completely non-functional — clicking Edit did nothing</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning the Content/CMS group: openEditModal() ends with document.getElementById("editModal").style.display = "block", but there was no element with id="editModal" anywhere on the live page — the &lt;form id="editForm"&gt; had lost its wrapping &lt;div id="editModal" class="modal"&gt; at some point (dead commented-out code directly above it in the same file still shows the wrapper, confirming it used to exist). Since getElementById("editModal") returned null, every click on "Edit" for any About section threw "Cannot set properties of null (reading 'style')" and did nothing — independent of anything in this redesign pass. Fixed by restoring the wrapping div. Also fixed a second bug on the same action: the Edit button passed only 5 of the 6 arguments openEditModal() expects, so imageUrl was always undefined and the modal's current-image preview never worked even once the modal itself could open — added the missing argument using the correct column name (section_image, confirmed against the schema; not image_url, which doesn't exist on this table). Verified live: Edit modal now opens correctly with the right section loaded and CKEditor initialized.</t>
   </si>
   <si>
@@ -364,7 +370,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). Remaining: announcements.ejs — then Other (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Next up: Other group (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -965,11 +971,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
     </font>
     <font>
       <b/>
@@ -994,12 +1000,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1432,13 +1438,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1474,13 +1480,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="4">
         <v>15</v>
       </c>
       <c r="D9" s="4">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1491,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1549,8 +1555,8 @@
       <c r="B4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>20</v>
+      <c r="C4" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1563,8 +1569,8 @@
       <c r="B5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>20</v>
+      <c r="C5" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>25</v>
@@ -1577,11 +1583,11 @@
       <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1589,10 +1595,10 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>30</v>
@@ -1605,8 +1611,8 @@
       <c r="B8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>20</v>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>32</v>
@@ -1619,8 +1625,8 @@
       <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>20</v>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>34</v>
@@ -1633,8 +1639,8 @@
       <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>20</v>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>36</v>
@@ -1647,8 +1653,8 @@
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>20</v>
+      <c r="C11" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>38</v>
@@ -1661,8 +1667,8 @@
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>20</v>
+      <c r="C12" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>40</v>
@@ -1675,8 +1681,8 @@
       <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>20</v>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>42</v>
@@ -1689,8 +1695,8 @@
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>20</v>
+      <c r="C14" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>44</v>
@@ -1703,8 +1709,8 @@
       <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>20</v>
+      <c r="C15" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>46</v>
@@ -1745,8 +1751,8 @@
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>20</v>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>52</v>
@@ -1759,8 +1765,8 @@
       <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>20</v>
+      <c r="C19" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>54</v>
@@ -1768,27 +1774,27 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>20</v>
+      <c r="C21" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>59</v>
@@ -1796,13 +1802,13 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>20</v>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>61</v>
@@ -1810,13 +1816,13 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>20</v>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>63</v>
@@ -1824,13 +1830,13 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>20</v>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>65</v>
@@ -1838,13 +1844,13 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>20</v>
+      <c r="C25" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>67</v>
@@ -1852,13 +1858,13 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>20</v>
+      <c r="C26" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>69</v>
@@ -1866,13 +1872,13 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>20</v>
+      <c r="C27" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>71</v>
@@ -1880,13 +1886,13 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>20</v>
+      <c r="C28" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>73</v>
@@ -1894,13 +1900,13 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>20</v>
+      <c r="C29" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>75</v>
@@ -1913,8 +1919,8 @@
       <c r="B30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>20</v>
+      <c r="C30" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>77</v>
@@ -1927,8 +1933,8 @@
       <c r="B31" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>20</v>
+      <c r="C31" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>79</v>
@@ -1941,8 +1947,8 @@
       <c r="B32" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>20</v>
+      <c r="C32" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>81</v>
@@ -1955,8 +1961,8 @@
       <c r="B33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>20</v>
+      <c r="C33" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>83</v>
@@ -1969,8 +1975,8 @@
       <c r="B34" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>20</v>
+      <c r="C34" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>85</v>
@@ -2011,8 +2017,8 @@
       <c r="B37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>20</v>
+      <c r="C37" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>91</v>
@@ -2025,8 +2031,8 @@
       <c r="B38" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>20</v>
+      <c r="C38" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>93</v>
@@ -2034,35 +2040,35 @@
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>100</v>
@@ -2081,8 +2087,8 @@
       <c r="B42" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>20</v>
+      <c r="C42" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>103</v>
@@ -2090,27 +2096,27 @@
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>20</v>
+      <c r="C44" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>108</v>
@@ -2118,30 +2124,44 @@
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>20</v>
+      <c r="C46" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2180,13 +2200,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2194,83 +2214,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>118</v>
+        <v>130</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>118</v>
+        <v>132</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2291,13 +2311,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2305,1108 +2325,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>138</v>
+        <v>144</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>138</v>
+        <v>148</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>138</v>
+        <v>150</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>138</v>
+        <v>152</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>138</v>
+        <v>154</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>138</v>
+        <v>156</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>138</v>
+        <v>158</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>138</v>
+        <v>160</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>138</v>
+        <v>162</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>138</v>
+        <v>164</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>138</v>
+        <v>166</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>138</v>
+        <v>168</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>138</v>
+        <v>171</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>138</v>
+        <v>173</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>138</v>
+        <v>175</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>138</v>
+        <v>177</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>138</v>
+        <v>179</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>138</v>
+        <v>181</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>138</v>
+        <v>183</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>138</v>
+        <v>185</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>138</v>
+        <v>188</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>138</v>
+        <v>190</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>138</v>
+        <v>192</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>138</v>
+        <v>194</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>138</v>
+        <v>196</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>138</v>
+        <v>198</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>138</v>
+        <v>200</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>138</v>
+        <v>202</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>138</v>
+        <v>205</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>138</v>
+        <v>207</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>138</v>
+        <v>209</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>138</v>
+        <v>211</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>138</v>
+        <v>213</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>138</v>
+        <v>215</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>138</v>
+        <v>217</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>138</v>
+        <v>219</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>138</v>
+        <v>221</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>138</v>
+        <v>224</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>138</v>
+        <v>226</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>138</v>
+        <v>228</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>138</v>
+        <v>233</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>138</v>
+        <v>235</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>138</v>
+        <v>237</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>138</v>
+        <v>240</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>138</v>
+        <v>242</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>138</v>
+        <v>244</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>138</v>
+        <v>246</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>138</v>
+        <v>251</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>138</v>
+        <v>256</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>138</v>
+        <v>258</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>138</v>
+        <v>260</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>138</v>
+        <v>262</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>138</v>
+        <v>265</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>138</v>
+        <v>273</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>138</v>
+        <v>275</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>138</v>
+        <v>277</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>138</v>
+        <v>279</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>138</v>
+        <v>281</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>138</v>
+        <v>283</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>138</v>
+        <v>285</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>138</v>
+        <v>290</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>138</v>
+        <v>292</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>138</v>
+        <v>294</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>138</v>
+        <v>296</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>138</v>
+        <v>299</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>138</v>
+        <v>301</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>138</v>
+        <v>303</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>138</v>
+        <v>305</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>138</v>
+        <v>307</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>138</v>
+        <v>309</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="312">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Feedback Dashboard: search box visually overlapped and swallowed clicks on the Apply filter button</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: the search box used the shared .jk-search-wrap class with an inline style override (flex:1, no max-width) that dropped its normal 320px cap, and the shared .jk-search-input rule had no box-sizing:border-box, so the input's own padding (46px) added on top of its computed width instead of being included in it. Together these let the search box grow wide enough to visually sit on top of the Apply button — confirmed via a real Puppeteer click plus an elementFromPoint check at the button's coordinates, which landed on the search input, not the button. Clicking Apply therefore did nothing (confirmed: the user_type=student filter never even reached the API). Fixed at the shared CSS level (benefits every other page using .jk-search-input, none of which had visibly collided before only because they didn't override the max-width cap) and removed the inline override on this page. Verified live: a real click on Apply now correctly lands on the button and filters the table (6 of 13 rows for user_type=student, matching the backend's own correct filtering, which was never actually broken).</t>
+  </si>
+  <si>
     <t>CRITICAL: Announcements page's search box and status filter crashed the whole table, showing zero rows</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: public/js/admin-announcements.js had the entire search/filter/table-click-delegation logic duplicated near the end of the file. The duplicate searchInput 'keyup' and statusFilter 'change' listeners both called renderAnnouncements() with no argument, but renderAnnouncements(data) immediately does tableBody.innerHTML = "" then reads data.length — since the correct AND broken listeners both fired on every keystroke/change, typing in the search box or changing the status filter reliably cleared the table then threw "Cannot read properties of undefined (reading 'length')", leaving the table empty with no way to recover short of a page reload. Confirmed live via Puppeteer: pageErrors showed the exact TypeError and a search for a common letter returned 0 rows instead of the matching announcements. Also removed in the same cleanup: a dead no-op delegated click handler checking for .editBtn/.publishBtn/.archiveBtn/.deleteBtn classes and a data-id attribute the actual rendered buttons never have (they use .btn-view/.btn-edit/.btn-success/.btn-warning/.btn-danger with onclick attributes directly), and a redundant duplicate loadAnnouncements() call at the bottom of the file causing a double fetch on every page load. Also found every class used by this page's JS-rendered table rows and modals (.btn-success/.btn-warning/.btn-danger/.action-buttons/.priority/.status/.text-muted/.text-center/.large-modal/.modal-header/.modal-footer/.form-group/.checkbox-group) had zero matching CSS anywhere in the codebase — confirmed via a grep across every stylesheet — so this page's modals and action buttons were rendering essentially unstyled even before today. Added a page-scoped &lt;style&gt; block using jk-* tokens. Verified live after the fix: zero page errors, search returns correct row counts, status filter works, View modal opens with real data.</t>
   </si>
   <si>
@@ -370,7 +376,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Next up: Other group (feedback.ejs, analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs).</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Other group started: feedback.ejs shipped (stat grid, card grid kept as-is since it was already good, toolbar restyled) — found and fixed a real bug: the search box's inline style override removed its normal max-width cap and the shared input class was missing box-sizing:border-box, together letting the search box grow wide enough to visually cover and swallow clicks on the Apply filter button; fixed at the shared CSS level, see Known Issues. Remaining: analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1438,13 +1444,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,13 +1486,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="4">
         <v>15</v>
       </c>
       <c r="D9" s="4">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1497,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1541,11 +1547,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1553,10 +1559,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1597,11 +1603,11 @@
       <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1609,10 +1615,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>32</v>
@@ -1737,8 +1743,8 @@
       <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>20</v>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>50</v>
@@ -1751,8 +1757,8 @@
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>17</v>
+      <c r="C18" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>52</v>
@@ -1788,21 +1794,21 @@
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>60</v>
@@ -1816,7 +1822,7 @@
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>62</v>
@@ -1830,7 +1836,7 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
@@ -1844,7 +1850,7 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
@@ -1858,7 +1864,7 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
@@ -1872,7 +1878,7 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>70</v>
@@ -1886,7 +1892,7 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>72</v>
@@ -1900,7 +1906,7 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>74</v>
@@ -1914,7 +1920,7 @@
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>76</v>
@@ -2003,8 +2009,8 @@
       <c r="B36" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>20</v>
+      <c r="C36" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>89</v>
@@ -2017,8 +2023,8 @@
       <c r="B37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>17</v>
+      <c r="C37" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>91</v>
@@ -2054,41 +2060,41 @@
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>17</v>
+      <c r="C42" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>103</v>
@@ -2110,21 +2116,21 @@
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>109</v>
@@ -2138,21 +2144,21 @@
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>114</v>
@@ -2162,6 +2168,20 @@
       </c>
       <c r="D47" s="5" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2200,13 +2220,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2214,83 +2234,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2311,13 +2331,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2325,1108 +2345,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="316">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,27 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>CRITICAL: Admin Analytics page's Finance data (revenue, revenue chart, payment-status tables) 500'd on every single visit, and blocked the whole page</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: /admin/stats/finance's "school payments by status" query selected a status column directly from school_payments, but that table has no such column at all (confirmed via information_schema: id, school_id, quote_id, amount, created_at, payment_date) — status actually lives on the linked quotes row (paid/partial/unpaid), reached via quote_id. The query threw "column \"status\" does not exist" on every single call, independent of anything in this redesign pass. Worse, refreshAll()'s catch block shows a full-page blocking alert overlay on any fetch failure, and that overlay intercepted clicks on every other control on the page (confirmed via elementFromPoint: a real click aimed at the Refresh button landed on the alert's OK button instead) — so one broken query effectively froze the entire Analytics page on every load. Fixed by joining quotes for its real status column, matching the pattern already used on quotes.ejs/parentInvoices.ejs. Also fixed a second, independent bug found in the same function: loadFinance()'s event-payments summary table and the page's static "View Details" button + results container shared the same element id (eventPaymentsTableWrap), so loadFinance() (which always runs on page load via refreshAll()) unconditionally overwrote and destroyed the button before a user could ever click it — meaning Event Payment Details has never been reachable on this page. Gave the summary table its own id. Also fixed a cosmetic bug: a global, unscoped .charts CSS rule meant for an unrelated page was leaking a stray teal border onto this page's chart grid; renamed to .analytics-charts to avoid the collision. Verified live: finance endpoint now returns 200 with real revenue/payment data, no error overlay, Refresh button no longer overlapped, a real click on View Details now correctly loads and displays event payment records.</t>
+  </si>
+  <si>
+    <t>Admin Analytics page: the Range and School filter dropdowns don't do anything</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: neither dropdown's value is ever read anywhere in the page's JS, and none of the backend stat endpoints (overview/users/courses/finance/quizzes/activity) accept a date-range or school_id query param at all — confirmed via grep across adminController.js. Refresh always reloads the same fixed (unfiltered, all-time, all-schools) dataset regardless of what's selected. Unlike a dead link that 404s, this doesn't error — it's just decorative, so left in place rather than removed; building real backend date-range/school filtering is a genuine feature addition, out of scope for this styling/bug-fixing pass. Flagged here in case the client wants real filtering built.</t>
+  </si>
+  <si>
     <t>Feedback Dashboard: search box visually overlapped and swallowed clicks on the Apply filter button</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: the search box used the shared .jk-search-wrap class with an inline style override (flex:1, no max-width) that dropped its normal 320px cap, and the shared .jk-search-input rule had no box-sizing:border-box, so the input's own padding (46px) added on top of its computed width instead of being included in it. Together these let the search box grow wide enough to visually sit on top of the Apply button — confirmed via a real Puppeteer click plus an elementFromPoint check at the button's coordinates, which landed on the search input, not the button. Clicking Apply therefore did nothing (confirmed: the user_type=student filter never even reached the API). Fixed at the shared CSS level (benefits every other page using .jk-search-input, none of which had visibly collided before only because they didn't override the max-width cap) and removed the inline override on this page. Verified live: a real click on Apply now correctly lands on the button and filters the table (6 of 13 rows for user_type=student, matching the backend's own correct filtering, which was never actually broken).</t>
   </si>
   <si>
@@ -82,9 +97,6 @@
     <t>Gallery page: "Edit" link on every image is dead (404) — the feature was never implemented</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: each image card linked to /admin/gallery/edit/:id, but no such route is registered (routes/galleryRoutes.js only has upload/create-category/delete-image/delete-category) and galleryController.js exports no editImage function at all. This looks like a genuinely unimplemented feature (not a regression — there's nothing to regress from) rather than a bug, so building a real edit flow (change title/category/replace the image) is out of scope for a styling/bug-fixing pass. Removed the dead link for now rather than ship something that 404s. Flagged here in case the client wants the feature built properly later.</t>
   </si>
   <si>
@@ -376,7 +388,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Other group started: feedback.ejs shipped (stat grid, card grid kept as-is since it was already good, toolbar restyled) — found and fixed a real bug: the search box's inline style override removed its normal max-width cap and the shared input class was missing box-sizing:border-box, together letting the search box grow wide enough to visually cover and swallow clicks on the Apply filter button; fixed at the shared CSS level, see Known Issues. Remaining: analytics.ejs, dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Other group started: feedback.ejs shipped (stat grid, card grid kept as-is since it was already good, toolbar restyled) — found and fixed a real bug: the search box's inline style override removed its normal max-width cap and the shared input class was missing box-sizing:border-box, together letting the search box grow wide enough to visually cover and swallow clicks on the Apply filter button; fixed at the shared CSS level, see Known Issues. analytics.ejs shipped too (stat grid, toolbar, chart cards) — found and fixed a CRITICAL bug: the finance stats endpoint 500'd on every single visit (querying a nonexistent column), and because of how the page handles fetch failures, this blocking-overlayed and froze clicks across the ENTIRE page; also fixed a second bug where the finance load unconditionally destroyed the page's own "View Details" button via a duplicate element id, and a cosmetic global-CSS class collision; see Known Issues. The page's Range/School filter dropdowns are decorative (never wired to any backend param) — flagged as Pending rather than built out, since real date-range filtering is a feature addition out of scope here. Remaining: dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1444,13 +1456,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,13 +1498,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="4">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1503,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1547,11 +1559,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1559,10 +1571,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="7" t="s">
         <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1589,8 +1601,8 @@
       <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>27</v>
@@ -1617,11 +1629,11 @@
       <c r="B8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1629,13 +1641,13 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1643,10 +1655,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>36</v>
@@ -1757,8 +1769,8 @@
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>22</v>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>52</v>
@@ -1785,8 +1797,8 @@
       <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>17</v>
+      <c r="C20" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>56</v>
@@ -1808,35 +1820,35 @@
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>64</v>
@@ -1850,7 +1862,7 @@
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
@@ -1864,7 +1876,7 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
@@ -1878,7 +1890,7 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>70</v>
@@ -1892,7 +1904,7 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>72</v>
@@ -1906,7 +1918,7 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>74</v>
@@ -1920,7 +1932,7 @@
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>76</v>
@@ -1934,7 +1946,7 @@
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>78</v>
@@ -1948,7 +1960,7 @@
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>80</v>
@@ -2023,8 +2035,8 @@
       <c r="B37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>22</v>
+      <c r="C37" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>91</v>
@@ -2051,8 +2063,8 @@
       <c r="B39" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>17</v>
+      <c r="C39" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>95</v>
@@ -2074,55 +2086,55 @@
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>17</v>
+      <c r="C44" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>107</v>
@@ -2130,16 +2142,16 @@
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2147,41 +2159,69 @@
         <v>15</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="5" t="s">
+    </row>
+    <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>117</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2220,13 +2260,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2234,83 +2274,83 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2331,13 +2371,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -2345,1108 +2385,1108 @@
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/docs/jkthub-brd-status-checklist.xlsx
+++ b/docs/jkthub-brd-status-checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="318">
   <si>
     <t>JKT Hub — BRD Status Checklist</t>
   </si>
@@ -64,12 +64,18 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Database Tables page took ~34 seconds to load on every single visit</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Found while redesigning this page: adminDbController.js's showTables ran one sequential `await pool.query(SELECT COUNT(*) FROM table)` per table in a plain for-loop over all 85 tables in utils/allowedTables.js, one full round trip to the remote Postgres instance at a time. Measured via direct timing: ~34 seconds to load the page, every single visit, independent of anything else in this redesign pass. Fixed by replacing the serial loop with Promise.all so all 85 count queries fire concurrently instead of one-by-one (same queries, same results, just no longer artificially serialized) — re-measured at ~5.5 seconds after the fix, a ~6x improvement. Verified live: card grid still shows the correct per-table counts, same order, now loading in a few seconds instead of over half a minute.</t>
+  </si>
+  <si>
     <t>CRITICAL: Admin Analytics page's Finance data (revenue, revenue chart, payment-status tables) 500'd on every single visit, and blocked the whole page</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>Found while redesigning this page: /admin/stats/finance's "school payments by status" query selected a status column directly from school_payments, but that table has no such column at all (confirmed via information_schema: id, school_id, quote_id, amount, created_at, payment_date) — status actually lives on the linked quotes row (paid/partial/unpaid), reached via quote_id. The query threw "column \"status\" does not exist" on every single call, independent of anything in this redesign pass. Worse, refreshAll()'s catch block shows a full-page blocking alert overlay on any fetch failure, and that overlay intercepted clicks on every other control on the page (confirmed via elementFromPoint: a real click aimed at the Refresh button landed on the alert's OK button instead) — so one broken query effectively froze the entire Analytics page on every load. Fixed by joining quotes for its real status column, matching the pattern already used on quotes.ejs/parentInvoices.ejs. Also fixed a second, independent bug found in the same function: loadFinance()'s event-payments summary table and the page's static "View Details" button + results container shared the same element id (eventPaymentsTableWrap), so loadFinance() (which always runs on page load via refreshAll()) unconditionally overwrote and destroyed the button before a user could ever click it — meaning Event Payment Details has never been reachable on this page. Gave the summary table its own id. Also fixed a cosmetic bug: a global, unscoped .charts CSS rule meant for an unrelated page was leaking a stray teal border onto this page's chart grid; renamed to .analytics-charts to avoid the collision. Verified live: finance endpoint now returns 200 with real revenue/payment data, no error overlay, Refresh button no longer overlapped, a real click on View Details now correctly loads and displays event payment records.</t>
   </si>
   <si>
@@ -388,7 +394,7 @@
     <t>Partially done</t>
   </si>
   <si>
-    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Other group started: feedback.ejs shipped (stat grid, card grid kept as-is since it was already good, toolbar restyled) — found and fixed a real bug: the search box's inline style override removed its normal max-width cap and the shared input class was missing box-sizing:border-box, together letting the search box grow wide enough to visually cover and swallow clicks on the Apply filter button; fixed at the shared CSS level, see Known Issues. analytics.ejs shipped too (stat grid, toolbar, chart cards) — found and fixed a CRITICAL bug: the finance stats endpoint 500'd on every single visit (querying a nonexistent column), and because of how the page handles fetch failures, this blocking-overlayed and froze clicks across the ENTIRE page; also fixed a second bug where the finance load unconditionally destroyed the page's own "View Details" button via a duplicate element id, and a cosmetic global-CSS class collision; see Known Issues. The page's Range/School filter dropdowns are decorative (never wired to any backend param) — flagged as Pending rather than built out, since real date-range filtering is a feature addition out of scope here. Remaining: dbTables.ejs, viewTable.ejs, adminProfile.ejs, classroom-students.ejs, parentChildren.ejs.</t>
+    <t>Client loved the School Details page redesign and asked for the same professional/gamified/branded treatment (jk-* design system: cream/gold palette, stat cards, card grids, pill badges, consolidated row-action buttons) across the entire admin panel, plus sortable column-header arrows on every data table. Inventoried all 42 files under views/admin/ — 3 are dead/unreachable code (left alone per client's choice), 3 are pre-auth pages (out of scope), leaving 36 real pages across 7 functional areas (Dashboard/System, Schools/Students, Courses/Pathways, Content/CMS, Commerce, Communication, Other). 21 of the 36 have real &lt;table&gt; elements (sort-arrow candidates); the rest are card-grids or single-record settings pages. Agreed order: Dashboard first (main landing page), then by usage frequency (Schools/Students next, then the rest). Infrastructure shipped first: (1) fixed the shared .sortable-table sort-arrow CSS (a pre-existing typo meant clicking a sortable header never visibly showed anything) with a guard so checkbox/icon-only-action columns don't get a pointless arrow — improved all 9 pages already using .sortable-table before any visual redesign touched them; (2) extracted the ~190-line jk-* CSS block out of school-details.ejs's inline &lt;style&gt; into a shared public/css/admin-jk-design-system.css linked platform-wide, so every future page gets these classes for free instead of copy-pasting; (3) found and fixed a real pre-existing bug surfaced by that extraction — .jk-select had no width override, so the browser's global `select{width:100%}` rule made every dropdown stretch full-width and stack vertically instead of sitting inline (already live on School Details' own Students/Teachers toolbars, just not visible there with only one dropdown per toolbar). Dashboard page (dashboard.ejs) is now FULLY SHIPPED, all 7 tabs: Overview, Business KPIs, Learning, Schools, Finance, Engagement, Reports &amp; Pitch Decks. The Reports tab's outer panels/toolbars/buttons/table were restyled but its deep Partnership Proposal form fields and photoPickerModal were deliberately left as-is (complex AI-drafting + photo-picker JS not worth the regression risk for a style-only pass) — flagged for a dedicated follow-up if wanted. Found and fixed 2 more real bugs along the way (Engagement tab's Filter button called an undefined function; input[type=date] fields needed a stronger CSS selector to get the same width fix selects already had) — see Known Issues. Verified every tab live against real platform data. Schools/Students page group: schools.ejs shipped (header card, 4 stat cards computed from existing data, sortable table with logo+name+email row, Edit modal restyled). students.ejs shipped too — this one was a bigger lift: it was the ONLY admin page not using the shared adminHeader.ejs partial (standalone HTML, no nav menu, a full duplicate copy of the sort-table JS); converting it onto the shared header surfaced a real bug (missing `role` local caused an immediate 500) now fixed, see Known Issues. archive.ejs shipped too (all 11 entity tabs restyled — lowest-risk page so far, its JS is entirely class/data-attribute driven so needed zero logic changes). classroom-dashboard.ejs shipped too (header card, Report Centre, 3 stat cards, all 4 tables, Chart.js canvas untouched). studentProgress.ejs explicitly skipped per client instruction (already well-designed with its own sp-* system, and shared with parent/school_admin roles — redesigning it risked an unwanted change to a non-admin-only page). studentEnrollments.ejs shipped (header card, 1 stat card, course table now sortable — previously had no sorting at all). schoolCourses.ejs shipped too (header card, per-school collapsible sections recolored to jk palette, term select/search/course-grid/save-button restyled, Courses-by-Term table converted to jk-table — all JS-dependent ids/classes kept unchanged). parentInvoices.ejs shipped too (header card, 8-card financial stat grid, Payment Trends chart, filter toolbar, sortable jk-table with pill status badges, 3 modals converted to jk-modal; also fixed a stray &lt;title&gt; bug showing "Quotes" instead of "Parent Invoices", and removed a dead unused custom sort function). quotes.ejs shipped too (same financial-analytics pattern as parentInvoices.ejs; removed the per-column onclick sort handlers and ⬍ suffixes in favor of the shared sortable-table mechanism; kept the existing payment-toggle status button classes untouched since the status filter JS reads them directly). editUser.ejs shipped too — and surfaced a real security-relevant bug while being redesigned: its Role dropdown compared against the wrong local (the logged-in admin's own role instead of the edited user's), always pre-selecting "Admin" and risking a silent privilege escalation on submit; fixed and verified against a real DB write, see Known Issues. Schools/Students group now fully shipped (9 pages). Courses/Pathways group started: courses.ejs shipped (header card, search + pathway-filter-tab toolbar, course cards restyled via a new additive .jk-course-card class that layers onto the existing .card-thumbnail markup rather than replacing it, so search/filter JS and the shared overview-curriculum-modal trigger needed zero changes; Create/Edit modals deliberately left untouched since they're each bound to a dynamically-created CKEditor instance and an outside-click handler keyed to the literal "modal" class). singleCourse.ejs is a bigger lift — it's a shell page delegating 6 tabs to separate partials (courseDetails/modules/lessons/courseAssignment/courseProject/courseExternalProjects, ~1885 lines total), being redesigned tab-by-tab: shell + Course Details tab shipped (header card with thumbnail/level/price, stat grid, curriculum panel), Modules tab shipped too (same jk-course-card pattern as courses.ejs). Found and fixed a real, independently pre-existing bug along the way: a global openModal()/closeModal() name collision between singleCourse.ejs's own dead leftover code and modules.ejs's real implementation meant "+ Add Module" has been completely broken (threw an error, did nothing) on every course — see Known Issues. Lessons tab shipped too (header/toolbar restyled, lesson cards get the same jk-course-card treatment; all 5 modals — Add/Edit Lesson, Manage Quiz, Manage Lab, AI Quiz Preview — deliberately untouched, this is the most JS/CKEditor-heavy tab in the whole admin panel). Assignment tab shipped too — found and fixed a real bug: the AJAX-create card template was missing a paragraph the server-rendered card had, so the edit-success handler's position-based DOM patch (p:nth-of-type(2)) corrupted the wrong paragraph for pre-existing assignments; fixed with a stable class selector, see Known Issues. Capstone Project tab shipped too — removed a page-local &lt;style&gt; block that duplicated and diverged from the shared global modal styling, and caught+fixed a regression of its own (that local CSS was also the only thing giving the edit modal its display:none default; replaced with an inline style on the element). External Projects tab shipped too, completing singleCourse.ejs's full 6-tab redesign (Details/Modules/Lessons/Assignment/Project/External Projects) — 3 real pre-existing bugs found and fixed across the tabs in total (broken Add Module, an edit-DOM-patch mismatch, a missing null-check crash). pathways.ejs shipped too (header card, pathway cards get the jk-course-card treatment; found and fixed a real bug — a duplicate id attribute on the Description textarea meant that field's CKEditor silently never initialized in every pathway's edit modal, see Known Issues). pathwayCourses.ejs shipped too (same jk-course-card pattern; found and fixed the same imageInput null-check crash as singleCourse.ejs, plus removed several duplicate/dead function declarations). guides.ejs shipped too (6 guide sections restyled to jk-report-panel; found and removed a broken "+ Add Assignment" button calling a function that only exists on a different, unrelated partial — threw "not defined" and did nothing). Courses/Pathways functional area is now FULLY SHIPPED — 6 real pre-existing bugs found and fixed across the whole group (see Known Issues). Content/CMS group started: editFaq.ejs, manageFaqs.ejs, manageTestimonies.ejs shipped (jk-report-panel cards, jk-pill status badges). Found and fixed editFaq.ejs's invalid doubly-nested HTML (its own full document shell AND an adminHeader.ejs include, which also has one) and a dead CKEDITOR.replace() call on manageFaqs.ejs. Also fixed .jk-btn-outline/.jk-btn-outline-sm in the shared stylesheet (missing display:inline-flex + white-space:nowrap caused a button to stretch to its flex row's full height and wrap its label when used without explicit align-items) — spot-checked against already-shipped schools.ejs/quotes.ejs to confirm no regression. company.ejs shipped too — and found a CRITICAL pre-existing bug: /admin/company has been throwing a 500 on every single load (a controller referenced an undeclared variable, `infoResult`), completely unrelated to this redesign pass but discovered while touching the page; fixed, see Known Issues. Also fixed the Hero Image field being wrongly `required` on an edit form (forced a re-upload on every unrelated save) and 3 fields sharing one duplicate id="content". benefits.ejs shipped too (same jk-course-card pattern; fixed the same imageInput null-check crash pattern as before, plus removed a dead CKEditor call and a dead filterByPathway function — this is now the 3rd occurrence of the imageInput crash across pages, seems to have been copy-pasted around). editAbout.ejs shipped too — found ANOTHER critical pre-existing bug: Edit About Section was completely non-functional (openEditModal() referenced a #editModal element that didn't exist on the page at all, a lost wrapper div), independent of this redesign; fixed, see Known Issues. Also fixed a second bug on the same action (missing 6th argument meant the image preview never worked). gallery.ejs shipped too — found and removed a dead "Edit" link on every image (no route/controller for it exists at all, a genuinely unimplemented feature, not a regression — flagged as a Pending gap rather than built out of scope). Also removed several dead/duplicate function declarations. projectGalleryModeration.ejs shipped too (fully AJAX-driven page — restyled the static shell/toolbar/table-header CSS and reused the .login-tabs pattern without touching any JS logic or the dynamically-generated row/modal HTML in its JS template strings). This completes the Content/CMS group (8 pages: editFaq, manageFaqs, manageTestimonies, company, benefits, editAbout, gallery, projectGalleryModeration) — 4 critical/significant pre-existing bugs found and fixed along the way (Company Info page crashing on every load, Edit About Section completely non-functional, Edit FAQ's doubly-nested HTML, a dead unimplemented gallery-image Edit link), see Known Issues. Commerce group shipped: pricingPlans.ejs — a deliberately light-touch pass, since this page already had its own excellent, genuinely gamified tier-badge plan-card system (Bronze/Silver/Gold/Diamond, ribbon, hover lift) that's better than a generic jk-course-card grid would be, so only the surrounding chrome (header card, section heads, create buttons) moved onto jk-*, cards left untouched. Communication group in progress: events.ejs shipped (jk-table + sortable headers; found and fixed a real bug — CKEDITOR.replace() was called twice for every editor on the page, once for the create form and once per event's edit form, duplicated verbatim later in the file). eventRegistrations.ejs shipped too (jk-table, search/export toolbar, payment-status pills). newsletters.ejs shipped too (8-card stat grid, jk-table; found and wired up a dead search/status-filter toolbar that had no id or JS listener at all — added straightforward client-side filtering). announcements.ejs shipped too — found and fixed a CRITICAL pre-existing bug: the search box and status filter crashed the whole table to zero rows (a duplicated, broken listener block in admin-announcements.js), plus a large set of this page's JS-rendered classes had zero CSS anywhere in the codebase; see Known Issues. This completes the Communication group (4 pages: events, eventRegistrations, newsletters, announcements). Other group started: feedback.ejs shipped (stat grid, card grid kept as-is since it was already good, toolbar restyled) — found and fixed a real bug: the search box's inline style override removed its normal max-width cap and the shared input class was missing box-sizing:border-box, together letting the search box grow wide enough to visually cover and swallow clicks on the Apply filter button; fixed at the shared CSS level, see Known Issues. analytics.ejs shipped too (stat grid, toolbar, chart cards) — found and fixed a CRITICAL bug: the finance stats endpoint 500'd on every single visit (querying a nonexistent column), and because of how the page handles fetch failures, this blocking-overlayed and froze clicks across the ENTIRE page; also fixed a second bug where the finance load unconditionally destroyed the page's own "View Details" button via a duplicate element id, and a cosmetic global-CSS class collision; see Known Issues. The page's Range/School filter dropdowns are decorative (never wired to any backend param) — flagged as Pending rather than built out, since real date-range filtering is a feature addition out of scope here. dbTables.ejs and viewTable.ejs shipped too (card grid + full CRUD table/modals restyled, all ids/form-actions/onclick wiring kept unchanged) — found and fixed a real performance bug: dbTables.ejs ran 85 sequential COUNT(*) queries (one per table) taking ~34s to load on every visit; parallelized with Promise.all, now ~5.5s; see Known Issues. Remaining: adminProfile.ejs, classroom-students.ejs, parentChildren.ejs.</t>
   </si>
   <si>
     <t>School Details page redesign (Phase 5: Attendance tab)</t>
@@ -1456,13 +1462,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
       <c r="D5">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1498,13 +1504,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C9" s="4">
         <v>16</v>
       </c>
       <c r="D9" s="4">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1515,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1559,11 +1565,11 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1571,10 +1577,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
@@ -1601,8 +1607,8 @@
       <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>20</v>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>27</v>
@@ -1615,8 +1621,8 @@
       <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
+      <c r="C7" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -1657,11 +1663,11 @@
       <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1669,10 +1675,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>38</v>
@@ -1797,8 +1803,8 @@
       <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>20</v>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>56</v>
@@ -1811,8 +1817,8 @@
       <c r="B21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>17</v>
+      <c r="C21" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>58</v>
@@ -1848,21 +1854,21 @@
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>66</v>
@@ -1876,7 +1882,7 @@
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>68</v>
@@ -1890,7 +1896,7 @@
     </row>
     <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>70</v>
@@ -1904,7 +1910,7 @@
     </row>
     <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>72</v>
@@ -1918,7 +1924,7 @@
     </row>
     <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>74</v>
@@ -1932,7 +1938,7 @@
     </row>
     <row r="30" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>76</v>
@@ -1946,7 +1952,7 @@
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>78</v>
@@ -1960,7 +1966,7 @@
     </row>
     <row r="32" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>80</v>
@@ -1974,7 +1980,7 @@
     </row>
     <row r="33" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>82</v>
@@ -2063,8 +2069,8 @@
       <c r="B39" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>20</v>
+      <c r="C39" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>95</v>
@@ -2077,8 +2083,8 @@
       <c r="B40" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>17</v>
+      <c r="C40" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>97</v>
@@ -2114,41 +2120,41 @@
     </row>
     <row r="43" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>17</v>
+      <c r="C45" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>109</v>
@@ -2170,21 +2176,21 @@
     </row>
     <row r="47" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>115</v>
@@ -2198,21 +2204,21 @@
     </row>
     <row r="49" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>120</v>
@@ -2222,6 +2228,20 @@
       </c>
       <c r="D50" s="5" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2260,13 +2280,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2274,83 +2294,83 @@
         <v>15</v>
       </c